--- a/관리/WBS(작업분할구조도)_v1.xlsx
+++ b/관리/WBS(작업분할구조도)_v1.xlsx
@@ -2256,14 +2256,18 @@
       <c r="H9" s="4">
         <v>2</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>196</v>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J9" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>201</v>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카테고리 6종 확정 (계약·약관 명칭 변경은 미결정)</t>
+        </is>
       </c>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
@@ -2472,14 +2476,18 @@
       <c r="H15" s="4">
         <v>7</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>255</v>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90%</t>
+        </is>
       </c>
       <c r="J15" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>257</v>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이슈 37건 · 결정사항 29건 반영. 최종 정리 남음</t>
+        </is>
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
@@ -2653,14 +2661,18 @@
       <c r="H20" s="4">
         <v>2</v>
       </c>
-      <c r="I20" s="18">
-        <v>1</v>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J20" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>284</v>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERD.png 업로드 완료</t>
+        </is>
       </c>
       <c r="L20" s="10"/>
       <c r="M20" s="10"/>
@@ -2692,13 +2704,19 @@
       <c r="H21" s="4">
         <v>2</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>287</v>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90%</t>
+        </is>
       </c>
       <c r="J21" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5화면 · 캡처 7장 · 흐름도 완료. PDF 저장 남음</t>
+        </is>
+      </c>
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
       <c r="N21" s="4"/>
@@ -4191,8 +4209,10 @@
       <c r="H64" s="4">
         <v>2</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>370</v>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J64" s="5" t="s">
         <v>315</v>
@@ -4228,14 +4248,18 @@
       <c r="H65" s="4">
         <v>1</v>
       </c>
-      <c r="I65" s="4" t="s">
-        <v>370</v>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J65" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="K65" s="5" t="s">
-        <v>424</v>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PageResponse 사용</t>
+        </is>
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="10"/>
@@ -4267,14 +4291,18 @@
       <c r="H66" s="4">
         <v>1</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>370</v>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J66" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="K66" s="5" t="s">
-        <v>138</v>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일명 + 본문 부분검색. 공백 정규화 포함 (ISS-034)</t>
+        </is>
       </c>
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
@@ -4306,14 +4334,18 @@
       <c r="H67" s="4">
         <v>1</v>
       </c>
-      <c r="I67" s="4" t="s">
-        <v>370</v>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J67" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="K67" s="5" t="s">
-        <v>431</v>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">filename*=UTF-8''. 줄바꿈 버그 ISS-016 수정</t>
+        </is>
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
@@ -4345,13 +4377,19 @@
       <c r="H68" s="4">
         <v>1</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>370</v>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J68" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="K68" s="5"/>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 18 변경으로 구현. cascade + 업로드 파일 제거</t>
+        </is>
+      </c>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
@@ -4407,13 +4445,19 @@
       <c r="H70" s="4">
         <v>2</v>
       </c>
-      <c r="I70" s="4" t="s">
-        <v>370</v>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J70" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="K70" s="5"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블 + 검색 + 페이징</t>
+        </is>
+      </c>
       <c r="L70" s="4"/>
       <c r="M70" s="10"/>
       <c r="N70" s="10"/>
@@ -4444,13 +4488,19 @@
       <c r="H71" s="4">
         <v>1</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>370</v>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J71" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="K71" s="5"/>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원문 접기·펼치기 + 분석 이력</t>
+        </is>
+      </c>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="10"/>
@@ -4481,8 +4531,10 @@
       <c r="H72" s="4">
         <v>1</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>370</v>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J72" s="5" t="s">
         <v>444</v>
@@ -4568,14 +4620,18 @@
       <c r="H75" s="4">
         <v>1</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>370</v>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J75" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="K75" s="5" t="s">
-        <v>450</v>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03 관통 확인</t>
+        </is>
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
@@ -4607,13 +4663,19 @@
       <c r="H76" s="4">
         <v>2</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>370</v>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J76" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="K76" s="5"/>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-016 · ISS-017</t>
+        </is>
+      </c>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="10"/>
@@ -4669,14 +4731,18 @@
       <c r="H78" s="4">
         <v>1</v>
       </c>
-      <c r="I78" s="4" t="s">
-        <v>370</v>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J78" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="K78" s="5" t="s">
-        <v>81</v>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66항목 전 항목 판정 완료</t>
+        </is>
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
@@ -4708,13 +4774,19 @@
       <c r="H79" s="4">
         <v>1</v>
       </c>
-      <c r="I79" s="4" t="s">
-        <v>370</v>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80%</t>
+        </is>
       </c>
       <c r="J79" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="K79" s="5"/>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건은 08-06 오전</t>
+        </is>
+      </c>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
@@ -4745,14 +4817,18 @@
       <c r="H80" s="4">
         <v>2</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>464</v>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J80" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="K80" s="5" t="s">
-        <v>466</v>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이슈관리 시트 37건 기록</t>
+        </is>
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
@@ -5075,14 +5151,18 @@
       <c r="H90" s="4">
         <v>1</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>370</v>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
       </c>
       <c r="J90" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="K90" s="5" t="s">
-        <v>490</v>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05 코드 프리즈. 이후 산출물 작업만 진행</t>
+        </is>
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
@@ -5250,46 +5330,2021 @@
       <c r="S94" s="20"/>
     </row>
     <row r="95" spans="1:19" ht="16.5" customHeight="1"/>
-    <row r="96" spans="1:19" ht="16.5" customHeight="1"/>
-    <row r="97" ht="16.5" customHeight="1"/>
-    <row r="98" ht="16.5" customHeight="1"/>
-    <row r="99" ht="16.5" customHeight="1"/>
-    <row r="100" ht="16.5" customHeight="1"/>
-    <row r="101" ht="16.5" customHeight="1"/>
-    <row r="102" ht="16.5" customHeight="1"/>
-    <row r="103" ht="16.5" customHeight="1"/>
-    <row r="104" ht="16.5" customHeight="1"/>
-    <row r="105" ht="16.5" customHeight="1"/>
-    <row r="106" ht="16.5" customHeight="1"/>
-    <row r="107" ht="16.5" customHeight="1"/>
-    <row r="108" ht="16.5" customHeight="1"/>
-    <row r="109" ht="16.5" customHeight="1"/>
-    <row r="110" ht="16.5" customHeight="1"/>
-    <row r="111" ht="16.5" customHeight="1"/>
-    <row r="112" ht="16.5" customHeight="1"/>
-    <row r="113" ht="16.5" customHeight="1"/>
-    <row r="114" ht="16.5" customHeight="1"/>
-    <row r="115" ht="16.5" customHeight="1"/>
-    <row r="116" ht="16.5" customHeight="1"/>
-    <row r="117" ht="16.5" customHeight="1"/>
-    <row r="118" ht="16.5" customHeight="1"/>
-    <row r="119" ht="16.5" customHeight="1"/>
-    <row r="120" ht="16.5" customHeight="1"/>
-    <row r="121" ht="16.5" customHeight="1"/>
-    <row r="122" ht="16.5" customHeight="1"/>
-    <row r="123" ht="16.5" customHeight="1"/>
-    <row r="124" ht="16.5" customHeight="1"/>
-    <row r="125" ht="16.5" customHeight="1"/>
-    <row r="126" ht="16.5" customHeight="1"/>
-    <row r="127" ht="16.5" customHeight="1"/>
-    <row r="128" ht="16.5" customHeight="1"/>
-    <row r="129" ht="16.5" customHeight="1"/>
-    <row r="130" ht="16.5" customHeight="1"/>
-    <row r="131" ht="16.5" customHeight="1"/>
-    <row r="132" ht="16.5" customHeight="1"/>
-    <row r="133" ht="16.5" customHeight="1"/>
-    <row r="134" ht="16.5" customHeight="1"/>
-    <row r="135" ht="16.5" customHeight="1"/>
+    <row r="96" spans="1:19" ht="18" customHeight="1">
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추가 반영 (08-03 ~ 08-05) — 정렬 시 각 ID 위치로 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="18" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.6</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기획</t>
+        </is>
+      </c>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">샘플 문서 수집 (카테고리별)</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80%</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 문서</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회의록·공지사항·보고서·계약서·메뉴얼 확보. 기타 1건 미확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="18" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.10</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개발환경</t>
+        </is>
+      </c>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드 프로젝트 초기 구성 (Vite + React)</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend/ 구조</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="18" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.11</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개발환경</t>
+        </is>
+      </c>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt 의존성 정리 및 중복 제거</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-004 · ISS-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="18" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.12</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개발환경</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개인 실행 환경 분리 (compose override)</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker-compose.override.yml</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-031 · ISS-032. 결정사항 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="18" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.9</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 보안 강화 (UUID 저장 + 경로 조작 방지)</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extraction_service.py</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="18" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.10</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 텍스트 + 이미지 OCR 통합 추출 (좌표 병합)</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py · layout.py</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 픽셀 → PDF 좌표 변환. ExtractMethod.HYBRID 산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" spans="1:19" ht="18" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.11</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동시 요청 시 엔진 충돌 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="1:19" ht="18" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.12</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외 처리</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 결과 실패 처리. HWPX 내부 이미지 오류는 건너뜀</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="18" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.13</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS)</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config.py · extractor</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-010 · 결정사항 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" spans="1:19" ht="18" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.14</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증 로직 · error_codes</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="18" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.15</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesseract 추출기 구현</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tesseract_extractor.py</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국어·영어 학습 데이터. Dockerfile apt 패키지 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" spans="1:19" ht="18" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.16</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진 비교 API</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_compare_router · service</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 1 근거 확보용</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" spans="1:19" ht="18" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.17</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 추출기 추가 및 비교 대상 확장</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">easyocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 6종으로 확장. CPU 전용 torch 고정 (ISS-030)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="1:19" ht="18" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.18</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 레이어 같은 줄 병합</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-020. 줄 단위 요소화 후 병합</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="18" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.19</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 정확도 측정 방식 개선 (정답 데이터 기반)</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_ground_truth.py</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편집거리 기반. 결정사항 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" spans="1:19" ht="18" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.20</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 입력 형식 확장 (문서 → 이미지 변환)</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_compare_image_loader.py</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" spans="1:19" ht="18" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.21</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 품질 분석 기반 전처리 동적 선택</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preprocessing.py · ocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">품질 측정 후 필요한 단계만 적용. 처리 시간 3배 증가 (ISS-036)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" spans="1:19" ht="18" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.22</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 PDF 읽기 순서 처리</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reading_order.py</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다단 문서 순서 복원. 표 영역 오인식 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="18" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.23</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 메모리 격리 (별도 프로세스)</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">easyocr_subprocess_extractor.py · workers/</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-035. 호출 종료 시 메모리 완전 회수</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="18" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.3</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 미리보기 + 추출 텍스트 비교 화면</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본프로젝트 '영역별 수정' 기능의 읽기 전용 선행 구현</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="18" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.4</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면 재구성 (드롭존 + 3단계 진행)</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목업 안3 반영. 공통 컴포넌트 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" spans="1:19" ht="18" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.5</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 화면</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OcrComparePage</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ocr-compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="18" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.8</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">openai_client.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="18" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.9</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약·분류 병렬 실행 최적화</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis_service.py</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-018. asyncio.gather 로 응답 시간 단축</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="18" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.10</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 실연동 전환 (FAKE → 실제 호출)</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.env · compose override</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-031 해결 후 전환. 요약·분류·근거 정상 생성 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="18" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2.3</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="18" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.4</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공통 컴포넌트 + 디자인 토큰</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tokens.css · Badge · Spinner · ErrorBanner</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:19" ht="18" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.5</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App.jsx 라우터 통합</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App.jsx</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-028. useState 토글 → react-router</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" spans="1:19" ht="18" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.6</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록에 업로드 진입점 추가</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ListPage</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" spans="1:19" ht="18" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.7</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 + 상세 패널 (마스터-디테일)</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ListPage</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 20. DocumentDetail 수정 없이 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" spans="1:19" ht="18" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.8</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레이아웃 폭·여백 통일 및 헤더 정리</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tokens.css · MainLayout</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨테이너 1440px. --c-page-x 변수화</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" spans="1:19" ht="18" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.9</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홈 화면 기능 설명 영역 구성</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능 확장 시 안내서 역할. 운영 메뉴얼과 문구 공유</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" spans="1:19" ht="18" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.10</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 공백 정규화</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">document_repository.py</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-034. 중복 구현 통합 (결정사항 28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" spans="1:19" ht="18" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.11</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 화면 (확인 창 · 목록 갱신)</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ListPage · DetailPage · DocumentDetail</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" spans="1:19" ht="18" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.12</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI/UX 전면 개선 및 공통 컴포넌트 리팩터링</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PageHeader · EmptyState · Icon · tokens.css</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반응형 구조 정리. 삭제 기능은 새 디자인 시스템으로 이식</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" spans="1:19" ht="18" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.13</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NotFoundPage.jsx</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 27. 종전 빈 화면 개선</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" spans="1:19" ht="18" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2.4</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-06</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-06</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SQL 로그 · 개선 전후 수치</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 17. 본프로젝트 이관 검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" spans="1:19" ht="18" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2.5</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-06</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60%</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비교 결과</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confidence 기반 측정 완료. 정답 데이터 기반 측정 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" spans="1:19" ht="18" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2.6</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">csv · xlsx</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-037. UTF-8 통일 · 이슈 단일 표 재번호 (결정사항 29)</t>
+        </is>
+      </c>
+    </row>
     <row r="136" ht="16.5" customHeight="1"/>
     <row r="137" ht="16.5" customHeight="1"/>
     <row r="138" ht="16.5" customHeight="1"/>
@@ -6238,11 +8293,15 @@
       <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>31</v>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본 파일. 이슈 37건 · 결정사항 29건 반영</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" customHeight="1">
@@ -6261,11 +8320,15 @@
       <c r="E6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>49</v>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERD.png 업로드 완료</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18" customHeight="1">
@@ -6284,10 +8347,16 @@
       <c r="E7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5화면 · 캡처 7장 · 화면흐름도. PDF 저장 남음</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1">
       <c r="A8" s="4" t="s">
@@ -6305,11 +8374,15 @@
       <c r="E8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>81</v>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66항목 전 항목 판정 완료 (csv)</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1">
@@ -6328,11 +8401,15 @@
       <c r="E9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>90</v>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건 08-06 오전 (csv)</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:7" ht="18" customHeight="1">
@@ -6351,11 +8428,15 @@
       <c r="E10" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>108</v>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이슈관리 시트 37건 기록</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:7" ht="18" customHeight="1">
@@ -6466,42 +8547,276 @@
       <c r="E15" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1"/>
-    <row r="18" ht="16.5" customHeight="1"/>
-    <row r="19" ht="16.5" customHeight="1"/>
-    <row r="20" ht="16.5" customHeight="1"/>
-    <row r="21" ht="16.5" customHeight="1"/>
-    <row r="22" ht="16.5" customHeight="1"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">README 포함. 08-05 코드 프리즈</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당자별 구현 가이드</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">md</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IMPLEMENTATION_GUIDE.md (내부용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레이아웃 목업 3안</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">html</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회의용. 화면정의서 원천 자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 수집 가이드</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">md</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카테고리별 수집처 · 검수 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팀 회의 자료 (D4)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">md</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정 요청 6건</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행 보고 자료 (D4)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">md</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행률 · 리스크 · 본프로젝트 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면흐름도</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">svg</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면정의서 삽입용</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 문서 작성 안내</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">md</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위·통합 테스트 관점 구분 기준</t>
+        </is>
+      </c>
+    </row>
     <row r="23" ht="16.5" customHeight="1"/>
     <row r="24" ht="16.5" customHeight="1"/>
     <row r="25" ht="16.5" customHeight="1"/>
@@ -7547,595 +9862,1899 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>65</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">폴더명 대소문자 충돌 (BackEnd vs backend)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">머지 시 GitHub에 backend/와 BackEnd/ 두 폴더가 생길 위험. Windows에서는 동일하게 보임</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows는 대소문자 비구분이지만 Git은 구분. 추적 중 파일은 소문자로 처리되나 신규(untracked) 파일은 디스크 실제 이름으로 커밋됨</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2단계 rename(BackEnd→temp→backend) + git add에 소문자 경로 명시. 소문자 backend/frontend로 팀 통일</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:10" ht="60" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>65</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-002</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협업</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker 설정 3중 중복 작업</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팀원 2명과 팀장이 각각 docker-compose.yml / Dockerfile을 작성. 합계 2시간 이상 소요</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당 영역이 파일 단위로 정해지지 않은 상태에서 동시 작업</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당자별 파일 분리 규칙 수립(라우터·서비스). 공유 파일은 수정 즉시 커밋·푸시 + 채널 알림. 세 버전을 병합해 하나로 통일</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>65</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config.py import 실패</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from pydantic_settings import BaseSetting → ImportError</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pydantic-settings v2의 클래스명은 BaseSettings(복수형). v1 표기와 혼동</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BaseSettings로 수정. 설정 항목이 더 많은 버전을 기준으로 병합하고 APP_NAME/DEBUG 반영</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>65</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-004</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt가 git에서 binary로 인식</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warning: Cannot merge binary files. 충돌 마커 없이 한쪽 버전만 남음</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 앞에 BOM(Byte Order Mark)이 포함되어 텍스트로 인식되지 않음</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOM 없이 ASCII로 재저장. 전이 의존성 제거하고 직접 의존성만 명시</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:10" ht="60" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>65</v>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settings 인스턴스화 실패 (extra_forbidden)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.env에 DATABASE_URL 등을 추가하자 앱 기동 시 검증 에러</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pydantic-settings v2는 Settings 클래스에 선언되지 않은 .env 키를 기본적으로 거부</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.env의 모든 키를 Settings에 대문자 스네이크 필드로 선언</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B11" s="11">
-        <v>46236</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J11" s="11">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="16">
-        <v>46234</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" s="16">
-        <v>46234</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="16">
-        <v>46236</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J17" s="16">
-        <v>46236</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="16">
-        <v>46237</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J18" s="16">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" s="16">
-        <v>46237</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J19" s="16">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="16">
-        <v>46237</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J20" s="16">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B21" s="16">
-        <v>46237</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J21" s="16">
-        <v>46237</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="16">
-        <v>46238</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="H22" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J22" s="16">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="B23" s="16">
-        <v>46239</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>264</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="G23" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="J23" s="16">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="27" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="28" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="29" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="30" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="32" spans="1:10" ht="16.5" customHeight="1"/>
-    <row r="33" ht="16.5" customHeight="1"/>
-    <row r="34" ht="16.5" customHeight="1"/>
-    <row r="35" ht="16.5" customHeight="1"/>
-    <row r="36" ht="16.5" customHeight="1"/>
-    <row r="37" ht="16.5" customHeight="1"/>
-    <row r="38" ht="16.5" customHeight="1"/>
-    <row r="39" ht="16.5" customHeight="1"/>
-    <row r="40" ht="16.5" customHeight="1"/>
-    <row r="41" ht="16.5" customHeight="1"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-006</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PowerShell에서 한글 주석이 깨져 보임</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get-Content로 .py 파일을 읽으면 한글 주석이 알 수 없는 문자로 표시</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일은 UTF-8인데 Windows PowerShell 5.1의 Get-Content가 기본 ANSI(CP949)로 읽음. 파일 자체는 정상</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get-Content -Encoding UTF8 사용, 또는 docker compose exec api python -c로 컨테이너 안에서 확인</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="60" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-007</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF OCR 및 텍스트 추출 기능 구현</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스캔본 PDF와 이미지 기반 PDF에서 텍스트 추출이 불가능하거나 결과가 누락됨</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 처리 기능과 PDF 추출 로직이 구현되지 않음</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 텍스트 추출기와 OCR 기능을 구현하고 문서 인식 프로세스를 추가</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="60" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-008</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt 중복 정의 및 config.py 오타</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 초기 세팅 중 requirements.txt가 중복 정의되고 config.py에 오타가 있어 기동 실패</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당 영역이 정해지기 전 여러 명이 동시에 초기 파일을 작성</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중복 정의를 통합하고 오타를 정정. pytesseract 버전 고정도 함께 반영</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="60" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-009</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다중 문서 형식 OCR 처리 및 동시성 문제 개선</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">여러 사용자가 동시에 OCR을 요청하면 처리 지연 및 충돌 가능성이 발생</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진을 동시에 사용하는 구조로 인해 자원 충돌 발생</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF·DOCX·HWPX·이미지 추출 구조를 통합하고 공유 OCR Lock을 적용하여 안정성 확보</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="60" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-010</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설계</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분량 제한 기준을 페이지 수에서 글자 수로 전환</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOCX·HWPX 업로드 시 페이지 수가 정확히 산출되지 않아 MAX_PAGES로 분량을 제한할 수 없음</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOCX·HWPX는 흐름(flow) 기반 포맷으로 페이지 나눔이 렌더링 시점에 결정됨. PDF와 달리 파일 자체에 페이지 경계 정보가 없음</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAX_PAGES는 PDF 전용으로 유지하고 전 포맷 공통 상한으로 MAX_EXTRACTED_CHARS=45000 추가. 페이지 수 근사치 계산안은 기각. analyses.latency_ms 실측 후 수치 재조정 예정</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="60" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카테고리 분류 프롬프트의 JSON 예시에 문법 오류</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분류 프롬프트가 요구하는 JSON 예시에서 항목 구분자가 콤마가 아니라 마침표로 적혀 있었음</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프롬프트 작성 시 오기. LLM 응답을 파싱하는 단계에서야 드러날 문제였음</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실제 LLM 호출 전에 코드 검토로 발견해 수정. 장애가 발생하기 전에 차단한 사례</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="60" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-012</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보안</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 업로드 검증 및 저장 방식 개선</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 파일, 대용량 파일, 조작된 파일명을 통한 업로드 요청으로 서비스 오류 및 보안 위험 발생</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 단계의 입력값 검증과 저장 방식이 미흡함</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UUID 기반 파일 저장을 적용하고 파일명, 파일 크기, 빈 파일 검증을 추가하여 업로드 보안 강화</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="60" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-013</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 텍스트와 이미지 OCR 결과 통합</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 내부 이미지의 문자 정보가 분석 결과에서 누락되어 정확도가 낮음</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 추출과 이미지 OCR 결과를 별도로 처리함</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 텍스트와 이미지 OCR 결과를 하나의 결과로 통합하여 추출 정확도 향상</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="60" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-014</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외처리</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 추출 실패 및 HWPX 예외 처리 개선</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 추출 결과를 정상 처리하거나 HWPX 내부 이미지 오류 발생 시 전체 분석이 중단됨</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추출 실패 판정과 이미지별 예외 처리가 부족함</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 추출 결과를 실패로 처리하고 손상된 이미지만 제외하여 나머지 문서는 정상 처리하도록 개선</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="60" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-015</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 업로드 제한 및 검증 기준 개선</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOCX·HWPX 대용량 문서 분석 시 응답 시간이 길어지고 서버 부하가 증가함</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지 수 기준을 적용하기 어려워 문서 길이 제한이 없었음</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45,000자 제한을 적용하고 PDF 페이지 수를 업로드 단계에서 조기 검사하도록 개선</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="60" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-016</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약 .txt 다운로드 시 줄바꿈이 모두 사라짐</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다운로드한 파일을 열면 제목·구분선·카테고리·요약이 모두 한 줄로 붙어 출력됨</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">document_service.py에서 줄 단위 리스트를 "".join(lines)로 이어붙여 구분자가 빈 문자열이었음. HTTP 200과 한글 파일명이 정상이라 기존 검증을 통과함</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"\n".join(lines)로 수정. 검증 기준을 '응답 코드 확인'에서 '결과 파일을 열어 내용 확인'으로 변경하고 통합테스트 항목에 추가</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="60" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-017</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 상세 조회(GET /api/documents/{id}) 500 오류</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록·분석 API는 정상인데 상세 조회만 500. 브라우저 콘솔에는 CORS 오류로 표시되어 원인 파악이 지연됨</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AnalysisResponse.result에 validation_alias="result_json"이 지정되어 있어 result= 키워드로는 필드를 채울 수 없음(Pydantic v2는 별칭 지정 시 원래 이름으로 입력받지 않음). 또한 500 응답에는 CORS 헤더가 붙지 않아 브라우저가 CORS 문제로 표시함</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AnalysisResponse.model_validate(analysis)로 변경해 analysis_router.py와 방식을 통일. 필드를 개별 전달하지 않으므로 스키마에 컬럼이 추가돼도 재발하지 않음</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현·최재정</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="60" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-018</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약·분류 분석이 순차 실행되어 응답 지연이 2배</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약과 카테고리 분류를 함께 실행하면 두 호출 시간이 그대로 더해져 응답이 느림</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis_service에서 두 분석을 순차로 await 함</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asyncio.gather로 병렬 실행하도록 변경해 전체 응답 시간을 단축</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="60" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 및 선택형 AI 분석 기능 구현</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 결과를 비교하거나 원하는 결과만 선택하여 AI 분석을 수행할 수 없음</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 결과 선택 기능과 비교 UI가 제공되지 않음</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 화면과 선택형 AI 분석 기능을 구현하여 사용자 선택 기반 분석을 지원</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="60" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-020</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자간이 넓은 PDF에서 텍스트가 분리되어 본문 검색 실패</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'1. 제 안 자 :' 처럼 자간을 벌린 공문서에서 텍스트가 제 / 안 / 자 로 세로 분리되어 저장됨. '제안자'로 검색하면 0건</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같은 줄 병합 로직이 OCR 경로(ocr_extractor)에만 적용되고 텍스트 레이어 경로(pdf_extractor)에는 없었음. 텍스트 요소를 블록 단위로 만들면서 x2·y2 좌표를 채우지 않아 병합 판정에 쓸 수 없었음</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 요소를 블록 단위에서 줄(line) 단위로 세분화하고 x2·y2 좌표를 채운 뒤 _merge_text_layer_elements()로 같은 줄을 병합. 이미 저장된 문서는 재업로드해야 반영됨</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라우터 연동 후 헤더가 두 개로 중복 표시</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홈 화면에서 공통 헤더(PDF Brief AI + 네비게이션) 아래에 Project Name 헤더가 한 번 더 표시됨</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면 통합 전 MainPage가 자체 &lt;header&gt;를 갖고 있었고, 공통 레이아웃(MainLayout)이 도입되면서 헤더가 두 번 그려짐</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage의 자체 헤더를 제거하고 그 안에 있던 사용자(로그인) 아이콘을 MainLayout 헤더로 이동. 모든 화면에서 로그인 진입점이 동일하게 보이도록 개선됨</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현·김보현</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 목록의 상세 패널에서 스크롤바가 2개 발생</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록에서 문서를 선택하면 페이지 스크롤과 패널 내부 스크롤이 동시에 생겨 조작이 불편함</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세 패널에 position: sticky와 높이 제한(max-height)을 함께 적용함. 패널이 화면보다 길어지면 위에 고정되어 아래쪽을 볼 수 없게 되고, 이를 보완하려 넣은 내부 스크롤이 페이지 스크롤과 겹침</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패널의 높이 제한·내부 스크롤을 제거하고 고정 대상을 긴 쪽(상세)에서 짧은 쪽(목록)으로 변경. 스크롤바 1개로 정리</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트 에러 안내 문구가 표시되지 않는 에러 코드 존재</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 분석 실패 시 사용자 보조 안내가 나타나지 않음</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트 안내 문구 매핑에 AI_CALL_FAILED로 적었으나 실제 정의된 코드는 AI_PROVIDER_ERROR. 존재하지 않는 키라 매칭되지 않음</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">error_codes.py의 ErrorCode 11종과 1:1로 대조해 매핑을 전면 정정하고, 파일 주석에 "키는 error_codes.py와 정확히 일치해야 한다"를 명시</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="60" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협업</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">main 직접 푸시로 인한 충돌 및 커밋 이력 오염</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같은 시점에 두 명이 프론트를 작업하던 중 충돌 발생. 해결 과정에서 동일한 커밋 메시지가 2건 생성되고, 한 팀원의 커밋에 다른 팀원의 변경분이 섞여 들어가 작업 주체 추적이 불가능해짐</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 9-1에서 feature/기능명 브랜치 전략을 정했으나 일정 압박으로 main에 직접 푸시함. 브랜치 격리가 없어 작업 중인 팀원이 즉시 영향을 받음</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 손실은 없었으나 우연에 의존한 결과였음. 기존 커밋은 재작성하지 않고 기록으로 유지(3인이 각자 pull한 상태와 어긋나면 더 큰 사고 위험). 잔여 작업을 feature/ui-polish 브랜치로 전환하여 규칙 복구</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pytesseract 의존성 버전이 고정되지 않음</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt의 다른 26개 패키지는 모두 ==로 버전이 고정되어 있으나 pytesseract만 버전 표기 없음</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesseract 비교 기능 추가 시 버전 명시 누락</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재빌드 시점에 따라 다른 버전이 설치되어 재현성이 깨질 수 있음. 버전 고정 요청</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="60" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지가 포함된 12페이지 PDF 추출에 55초 소요</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 후 응답까지 약 55초. 이미지 1장(ERD.png) 단독 업로드는 13초</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지 수가 아니라 OCR을 타는 이미지 개수에 비례. 13초 x 이미지 3~4개 = 55초</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가설 두 개를 측정으로 기각 — ① 확대 배율 상한(2.0) 적용 시 시간 변화 없음 ② PaddleOCR 보조 모델 3종 비활성화 시 오히려 16.7초. OCR 추론 비용 자체가 원인이므로 근본 개선은 본프로젝트로 이관. 미니프로젝트는 시연 시나리오로 대응</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본프로젝트 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전처리 도입 후 표 검출 좌표계 불일치로 표 병합 무력화</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외는 발생하지 않으나 표 병합이 전혀 동작하지 않음</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표 셀 좌표는 전처리된 이미지(최대 2배 확대) 기준, OCR 요소 좌표는 원본 기준으로 되돌려져 있어 cell.contains()가 매칭되지 않음. 두 기능이 서로 다른 브랜치에서 개발돼 자동 머지 시 좌표계 전제가 어긋남</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표 검출 입력을 전처리 전 원본 이미지로 변경해 좌표계를 통일. 자동 머지가 성공해도 좌표계·단위 같은 전제는 사람이 확인해야 한다</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="60" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-028</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App.jsx가 useState 토글 방식이라 일부 화면에 접근 불가</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ListPage·DetailPage·MainLayout이 이미 구현돼 있었는데도 화면 전환이 되지 않아 접근할 수 없었음</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App.jsx가 라우터 없이 useState 토글로 화면을 바꾸는 구조였음</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">react-router-dom으로 실제 라우팅을 연결해 모든 화면을 정상 접근 가능하게 함</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협업</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충돌 마커가 그대로 남은 채 커밋됨</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 작업 커밋과 레이아웃 정리 커밋이 충돌했고, &lt;&lt;&lt;&lt;&lt;&lt;&lt; HEAD 마커가 파일에 남은 상태로 커밋됨</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">충돌 해결을 마치지 않고 커밋. 자동 머지 결과를 확인하지 않음</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마커만 제거하지 않고, 팀원이 의도적으로 제거한 네비게이션 링크는 그대로 반영해서 정리. 한쪽을 무조건 살리지 않고 변경 의도를 확인함</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 설치 시 GPU용 CUDA 패키지가 함께 설치됨</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR을 추가하자 torch의 CUDA 패키지까지 딸려와 이미지 용량이 크게 늘어남</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">torch 기본 설치 인덱스가 GPU 판을 우선 제공. CPU 추론만 쓰는데도 GPU 의존성이 포함됨</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPU 전용 torch 인덱스를 먼저 설치하도록 Dockerfile을 수정하고 버전을 고정</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker-compose.yml이 .env 대신 .env.example을 읽어 로컬 설정이 반영되지 않음</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backend/.env에 API_KEY와 USE_FAKE_AI=false를 넣어도 컨테이너에 전달되지 않아 OpenAI 실연동이 불가</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose의 env_file이 ./backend/.env.example로 지정됨. 또한 .dockerignore에 .env가 있고 Dockerfile이 ./app만 복사하므로 컨테이너 안에 .env가 존재하지 않음</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개인 docker-compose.override.yml로 .env를 추가 로드(공유 파일 미수정). 정식 수정안은 env_file에 .env를 required: false로 추가하는 것 — 하위 호환이므로 .env가 없는 팀원에게 영향 없음. 팀 합의 후 반영 예정</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-032</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 3엔진 비교 실행 시 호스트 PC 강제 종료</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ocr-compare 실행 중 컴퓨터가 갑자기 꺼짐</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세 엔진(PaddleOCR·Tesseract·EasyOCR)이 모두 CPU 추론이며 PyTorch가 전 코어를 사용. docker-compose.yml에 CPU·메모리 제한이 없어 호스트 자원을 한계까지 사용 → 보호 종료</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개인 docker-compose.override.yml에 cpus·memory 제한 적용(팀원 PC 사양이 달라 공유 파일에는 넣지 않음). 발표 시연에서는 사전 측정 결과를 사용하고 실시간 실행하지 않음</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-033</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">환경</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">패키지 추가 후 프론트엔드 컨테이너에 반영되지 않음</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axios·react-router-dom 설치 후 이미지를 재빌드해도 컨테이너에서 모듈을 찾지 못함</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compose의 - /app/node_modules 익명 볼륨이 재사용되어 새 이미지의 node_modules를 낡은 볼륨이 덮어씀</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker compose up -d --build --force-recreate --renew-anon-volumes frontend로 볼륨까지 재생성. 이미지를 재빌드해도 컨테이너·볼륨이 낡으면 반영되지 않는다는 점을 팀 공유(백엔드 환경 변수도 같은 이유로 --force-recreate 필요)</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="60" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-034</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협업</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 공백 정규화가 두 명에게 중복 구현됨</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같은 문제를 두 사람이 각자 브랜치에서 해결해 document_repository.py에서 충돌</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이슈 공유 없이 각자 발견해 착수. 담당 파일 분리 규칙이 조회 로직에는 적용되지 않았음</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">먼저 올라온 팀원 코드를 기준으로 두고 빈 검색어 가드만 덧붙여 통합. git blame 이력을 보존하기 위해 덮어쓰지 않음</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현·김보현</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="60" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-035</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 호출 후 메모리가 회수되지 않고 상주</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR을 한 번만 사용해도 컨테이너 메모리 점유가 계속 유지됨</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PyTorch allocator가 해제한 메모리를 OS에 반환하지 않음. 인프로세스 캐시 해제(lru_cache 제거)만으로는 회수되지 않는 것을 실측으로 확인</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 추론을 별도 프로세스로 격리해 호출이 끝나면 메모리가 완전히 회수되도록 구현. 1차 조치가 효과 없음을 측정으로 확인한 뒤 접근을 바꾼 사례</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="60" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-036</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성능</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">품질 기반 자동 전처리 도입 후 OCR 처리 시간 3배 증가</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동일 이미지(ERD.png) 처리 시간이 12.7초에서 36.8초로 증가. 추출 글자 수는 955자에서 977자로 2.3% 증가</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 품질 분석 결과에 따라 upscale이 선택되어 픽셀 수가 4배가 됨. 임계값이 스캔본 기준이라 화면 캡처·디지털 문서에는 과하게 적용됨</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시간 3배 대비 정확도 2.3%로 문서 종류에 따라 손해. 문서 종류별 임계값 분리를 본프로젝트로 이관. 전처리가 비용을 지불하고 정확도를 사는 선택임을 수치로 확인한 사례</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="60" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-037</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 파일 인코딩·구조 손상 및 이슈 ID 중복</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위테스트결과서가 CP949로 저장되고 9개 열이 한 셀에 탭으로 뭉쳐 저장됨. 이슈관리 시트에는 표가 두 개 겹쳐 ID가 ISS-001~008 로 중복됨</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엑셀이 쉼표 구분 파일을 A열에 몰아서 열었고 그대로 저장함. 이슈 목록을 각자 작성해 아래에 붙여 넣으면서 번호 체계가 겹침</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9개 열로 복원하고 UTF-8(BOM)로 통일. 이슈관리는 단일 표로 통합하고 발생일 순으로 재번호. 산출물도 코드와 같은 병합 규칙이 필요함을 확인</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
     <row r="42" ht="16.5" customHeight="1"/>
     <row r="43" ht="16.5" customHeight="1"/>
     <row r="44" ht="16.5" customHeight="1"/>
@@ -9151,27 +12770,41 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>40</v>
+    <row r="5" spans="1:7" ht="60" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PaddleOCR v5를 본 추출 경로로 채택. Tesseract는 정확도 비교 검증용으로 병행 도입</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당자가 Docker 컨테이너에서 동작 테스트 완료. 기각 근거였던 "한국어 정확도 낮음"을 주장이 아니라 동일 문서를 여러 엔진으로 처리한 실측 결과로 입증하기 위해 비교 엔드포인트를 추가. 본 추출 경로는 PaddleOCR 단일 유지</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR / Tesseract 단독 사용</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정·박세현</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" customHeight="1">
@@ -9450,34 +13083,672 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A18" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="20" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="21" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="22" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="23" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="24" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="25" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="26" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="27" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="28" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="29" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="30" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="31" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="32" spans="1:7" ht="16.5" customHeight="1"/>
-    <row r="33" ht="16.5" customHeight="1"/>
-    <row r="34" ht="16.5" customHeight="1"/>
-    <row r="35" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:7" ht="60" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분량 제한 기준</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAX_PAGES 유지 + MAX_EXTRACTED_CHARS=45,000자 추가</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOCX·HWPX는 흐름 기반 포맷으로 페이지 수가 부정확. 글자 수는 모든 포맷에서 동일하게 산출됨. 45,000자는 담당자 제안값을 채택하고 latency_ms 실측 후 조정</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지 수 근사치 계산 / 20,000자 제한 / MAX_ANALYZE_CHARS 분리</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="60" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면 레이아웃</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 — 목록=안1(테이블), 상세=안2(우측 구성), 업로드=안3(드롭존)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안1·안2로 갈린 의견이 서로 다른 화면을 평가한 것으로 확인됨. DocumentDetail을 API 호출 없는 독립 컴포넌트로 분리해 전체화면·우측패널 양쪽에 재사용 가능하게 하여 전환 비용을 제거</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">안1 단일 채택 / 안2 단일 채택</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="60" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다크모드 지원</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미지원 (라이트 고정)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">index.css의 prefers-color-scheme 때문에 발표장 PC 설정에 따라 화면이 달라짐. 3인 화면의 색상 변수를 통일하는 추가 작업도 발생. 본프로젝트 개선 항목으로 이관</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OS 설정 연동 유지 / 다크모드 토글 제공</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="60" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드 스타일 관리</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3층 구조 — 디자인 토큰 / 공통 컴포넌트 / 각자 페이지</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSS 변수만 공유하면 버튼·배지가 화면마다 달라짐. 토큰(--c- prefix)과 공통 컴포넌트를 한 명이 소유해 일관성 확보. 기존 페이지 리팩토링은 강제하지 않아 진행 중 작업에 영향 없음. 실제로 다른 담당자가 새 화면에서 자발적으로 재사용함</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSS 변수만 공유 / 각자 자유 구현</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="60" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 클라이언트</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axios 도입. 기존 client.js는 수정하지 않고 http.js + document.js 신규 추가</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지시서의 "API 호출(Axios)" 요건을 충족하면서 다른 담당자 파일과 충돌 0. 인터셉터로 에러 응답(code/message/request_id)을 한 곳에서 정규화</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">client.js를 axios로 전면 교체 / fetch 유지</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="60" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 조회 N+1 쿼리</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선제 최적화하지 않고 테스트에서 실측한 뒤 개선</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서당 2회 추가 조회 발생(20건=41쿼리). SQL 로그로 수치를 확보한 뒤 개선하면 '발견 → 해결' 과정을 근거와 함께 제시할 수 있음</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초기 구현부터 벌크 조회(JOIN) 적용</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="60" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미니프로젝트 범위 제외</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.pdf 다운로드 / criteria_analyzer 미구현. 문서 삭제는 구현으로 변경(08-05)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지시서 플로우 ①~⑧에 삭제가 없어 처음에는 제외했으나, 테스트 과정에서 문서가 누적되어 목록 확인과 발표 시연이 어려워짐. DocumentRepository.delete()와 모델의 cascade 설정이 이미 있어 구현 비용이 낮았음(서비스·라우터·화면 버튼). 되돌릴 수 없는 동작이므로 확인 창을 거치도록 함</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 6종 전체 구현 / 데이터베이스에서 직접 삭제(SQL) — 개발자만 가능해 사용자 기능으로 성립하지 않음</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원·김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 진입점</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤더 네비게이션에서 제거하고 문서 목록의 버튼 하나로 통합</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드가 독립 메뉴로 분리되어 있어 목록 → 업로드 → 목록 왕복이 번거로움. 진입점을 목록으로 모아 목록 → 업로드 → 추출·분석 → 목록 한 방향 흐름을 만듦</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤더 메뉴 유지 / 목록에 모달로 업로드</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록·상세 표시 방식</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록에서 문서 선택 시 우측 패널에 상세 표시(마스터-디테일). 전체 화면 상세도 함께 유지</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 3건 기준 목록만으로는 화면이 비어 보임. 결정사항 13의 하이브리드를 실제로 구현한 형태이며 DocumentDetail을 수정 없이 재사용해 구현 비용이 낮았음</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 화면 상세만 유지 / 고정 플로팅 패널</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인증(로그인)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미니프로젝트 미구현. 삽입 지점만 확보</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지시서상 "회원가입 및 로그인(선택) — 없어도 됨". 구현 시 users 테이블·해싱·JWT·화면·토큰 저장·401 처리 및 기존 API 전체 재검증으로 6~10시간 소요. 필수 산출물(테스트·문서·발표) 미완 상태에서 선택 기능에 투입할 수 없음. 헤더 사용자 버튼과 라우트 트리에 삽입 지점을 확보해 화면 수정 없이 추가 가능</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 구현 / 프론트 화면만 구현(실제 인증 없음)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="60" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 전처리 범위</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6단계 + 프리셋 4종 (none / light / scan / full)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전처리는 정보를 깎는 트레이드오프이며 PaddleOCR(딥러닝)과 Tesseract(전통 알고리즘)의 최적 조합이 다름. 프리셋으로 분리해 측정 가능하게 함</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전처리 9종 일괄 적용 / 데이터 증강·정규화(학습용이라 추론에 부적합) / 색공간 변환·반전(문서 OCR에 무의미)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전처리와 좌표계</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좌표를 사용하는 경로는 전처리 후에도 원본 좌표계로 되돌려 반환. 회전(deskew)은 좌표 미사용 경로에서만 사용</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">확대·회전이 OCR 반환 좌표를 바꿔 호출 측의 좌표 변환과 어긋남. OcrExtractor 안에서 역변환을 끝내면 호출 측 수정이 불필요. 회전은 배율로 되돌릴 수 없어 프리셋으로 분리하고 안전장치(예외)로 오용을 차단</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">호출 측마다 좌표 보정 / 전처리에서 기하 변형 전면 배제</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현·최재정</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="60" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 정확도 측정 방식</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정답 데이터(LabelMe JSON) 기반 편집거리 정확도. 정답이 없으면 신뢰도 평균을 대용 지표로 사용</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각 엔진이 보고하는 confidence는 실제 오탈자를 반영하지 못해 엔진 비교 근거로 약함. 정답 텍스트와 대조하면 누락·삽입·오탈자가 모두 반영됨</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confidence 평균만 사용</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 입력 형식</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 6종 + PDF·DOCX·HWPX 허용 (문서는 첫 페이지·첫 이미지를 변환)</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비교용 이미지를 따로 만들어야 하는 번거로움 제거. 실제 업무 문서를 그대로 넣어 비교 가능</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 형식만 허용</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="60" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개인 실행 환경 설정</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker-compose.override.yml(gitignore)로 개인 설정 분리</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPU·메모리 제한은 PC 사양에 따라 달라 공유 파일에 넣으면 다른 팀원에게 손해. 로컬 .env 로드도 개인 환경에 해당</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공유 docker-compose.yml 직접 수정</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정의되지 않은 경로 처리</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">catch-all 라우트로 404 안내 화면 제공</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라우트가 5종만 정의되어 있어 그 밖의 주소로 접근하면 헤더조차 없는 빈 화면이 표시됨. 발표 중 주소를 잘못 입력하면 바로 드러나는 문제. NotFoundPage 추가로 안내와 복귀 경로를 제공</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 화면 유지(본프로젝트 이관) / 홈으로 자동 이동(오류 사실이 감춰짐)</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중복 구현 통합 원칙</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같은 문제를 두 명이 구현한 경우 먼저 올라온 코드를 기준으로 두고 보완만 덧붙인다</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 공백 정규화가 중복 구현되어 충돌. 나중에 올린 쪽이 덮어쓰면 git blame 이력이 사라져 작업 주체 추적이 불가능해짐. 먼저 올라온 코드를 살리고 빈 검색어 가드만 추가해 기능은 보강하고 이력은 보존</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나중 구현으로 전면 교체 / 각자 구현 유지 후 분기</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 파일 형식 통일</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSV는 UTF-8(BOM)·쉼표 구분으로 저장. 이슈관리 등 목록 시트는 담당자별 표를 따로 두지 않고 단일 표로 유지</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CP949로 저장된 파일이 다른 PC에서 깨지고, 엑셀이 열을 한 칸에 몰아 저장해 구조가 손상됨. 이슈 목록을 각자 작성해 붙여 넣어 ID가 중복됨. 산출물도 코드와 같은 병합 규칙이 필요</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당자별 시트 분리 / 파일 형식 자유</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+    </row>
     <row r="36" ht="16.5" customHeight="1"/>
     <row r="37" ht="16.5" customHeight="1"/>
     <row r="38" ht="16.5" customHeight="1"/>

--- a/관리/WBS(작업분할구조도)_v1.xlsx
+++ b/관리/WBS(작업분할구조도)_v1.xlsx
@@ -4827,7 +4827,7 @@
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이슈관리 시트 37건 기록</t>
+          <t xml:space="preserve">이슈관리 시트 46건 기록</t>
         </is>
       </c>
       <c r="L80" s="4"/>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">본 파일. 이슈 37건 · 결정사항 29건 반영</t>
+          <t xml:space="preserve">본 파일. 이슈 46건 · 결정사항 29건 반영</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이슈관리 시트 37건 기록</t>
+          <t xml:space="preserve">이슈관리 시트 46건 기록</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현·최재정</t>
+          <t xml:space="preserve">김보현·박세현</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -11755,15 +11755,469 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1"/>
-    <row r="43" ht="16.5" customHeight="1"/>
-    <row r="44" ht="16.5" customHeight="1"/>
-    <row r="45" ht="16.5" customHeight="1"/>
-    <row r="46" ht="16.5" customHeight="1"/>
-    <row r="47" ht="16.5" customHeight="1"/>
-    <row r="48" ht="16.5" customHeight="1"/>
-    <row r="49" ht="16.5" customHeight="1"/>
-    <row r="50" ht="16.5" customHeight="1"/>
+    <row r="42" spans="1:10" ht="60" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-038</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 결과에서 같은 줄 문자가 줄바꿈되어 출력</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같은 y 좌표에 있는 문자인데도 가로 간격이 벌어져 있으면 서로 다른 줄로 출력됨</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 이 반환하는 요소를 좌표 판정 없이 순서대로 이어붙였음. 세로 위치가 같은지 확인하는 단계가 없었다</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y 축 기준으로 서로 겹치는 문자를 한 줄로 병합하도록 변경</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="60" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-039</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(실행 취소) 가로 간격으로 본문과 표 영역을 분리하는 시도</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">줄 병합 후에도 자간이 넓은 문장이 다시 줄바꿈되어 나타남</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가로 간격이 크면 다른 영역으로 판단하도록 했으나, 자간을 벌린 공문서에서는 본문 안의 정상적인 간격까지 영역 경계로 오판함</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적용을 취소했다. 간격만으로는 '표의 열 구분'과 '넓은 자간'을 구별할 수 없다는 것을 확인하고, 선(line) 검출로 접근을 바꾸는 근거가 되었다 (ISS-040)</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="60" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-040</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표 영역을 인식하지 못해 표 내용이 뒤섞여 출력</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표가 포함된 문서에서 셀 값이 행 구분 없이 이어져 출력됨</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">간격 기반 판정(ISS-039)이 실패해 표 구조를 알 방법이 없었음</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenCV 로 표의 가로선·세로선을 검출해 셀 격자를 만들고, 셀 단위로 OCR 결과를 병합. 간격이라는 간접 신호 대신 실제로 그려진 선을 근거로 삼았다</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="60" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-041</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전처리 확대 시 이미지 비율이 왜곡됨</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 전처리에서 이미지를 확대하면 가로·세로 비율이 달라져 글자가 늘어남</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 크기에 맞추려고 가로와 세로를 각각 조정했음</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 비율을 유지한 채 확대하도록 수정. 확대 배율 상한도 함께 적용</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="60" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-042</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2단 구성 문서를 위에서 아래로만 읽어 순서가 뒤섞임</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단이 두 개인 문서에서 좌측 단과 우측 단의 문장이 번갈아 섞여 출력됨</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1차 시도 — 페이지 중앙의 연속된 세로 여백을 찾아 2단 여부를 판정했으나, 여백이 일정하지 않은 문서에서 단 구분에 계속 실패함</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">판정 방식을 폐기하고 Recursive XY-Cut(여백을 재귀적으로 잘라 블록을 나누는 방식)으로 전환. 이미지 파일에서 단 구분이 정상 동작함을 확인. 중앙 여백 탐색이라는 규칙 기반 접근의 한계를 측정으로 확인한 뒤 알고리즘을 바꾼 사례</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="60" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-043</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 레이어 PDF 의 읽기 순서 오류</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글자 정보가 있는 PDF 에서 단 구분 없이 위에서부터 훑어 읽어 순서가 어긋남</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recursive XY-Cut 이 OCR 경로에만 적용되어 있었고 텍스트 레이어 경로에는 없었음</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 레이어 추출에도 같은 알고리즘을 적용해 두 경로의 읽기 순서를 통일</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="60" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-044</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 PDF(텍스트 + 이미지)의 읽기 순서 미지원</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트와 이미지가 함께 있는 PDF 는 두 결과를 별도로 추출해 합치는 경로여서 단 순서 처리가 적용되지 않았음</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 경로와 OCR 경로가 각각 순서를 정한 뒤 합쳐지므로 전체 순서가 보장되지 않음</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 경로에도 Recursive XY-Cut 을 적용해 두 출처의 요소를 하나의 좌표계에서 함께 정렬하도록 변경</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="60" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-045</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버그</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표를 제목으로 오인식해 단 분리가 실패</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">표 아래 본문이 (y, x) 순서로 섞여 출력되고, 중앙 단 분리가 동작하지 않음</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지 상단 전체 폭을 차지하는 요소를 제목으로 보아 단 분리 대상에서 제외했는데, 표가 그 조건에 걸려 제목으로 판정됨</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">제목 보호 조건을 좁혀 실제 제목만 제외하도록 수정. OCR 이 만드는 단일 문자 노이즈도 본문에서 걸러냄</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해결</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="60" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-046</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결함</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비즈니스 오류가 서버 로그에 기록되지 않음</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응답의 request_id 로 서버 로그를 대조하려 했으나 해당 식별자가 로그에 없음. 404·409·413 등 정의된 오류 전부가 로그에 남지 않는다</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exceptions.py 의 핸들러 3종 중 validation_error_handler(422)와 unhandled_exception_handler(500)만 로그를 남기고, business_error_handler 에는 로그 호출이 없음. 에러 코드 11종 가운데 INTERNAL_ERROR 만 추적 가능한 상태</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">코드 프리즈(08-05) 이후 발견되어 이번 범위에서는 수정하지 않고 결함으로 기록한다. 조치안은 business_error_handler 에 logger.warning 한 줄 추가. request_id 생성·전달(미들웨어, X-Request-ID 헤더, 응답 본문)은 정상 동작하므로 로깅만 보완하면 추적이 가능해진다. 통합테스트 IT-PDF-07-4 에서 발견</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본프로젝트 이관</t>
+        </is>
+      </c>
+    </row>
     <row r="51" ht="16.5" customHeight="1"/>
     <row r="52" ht="16.5" customHeight="1"/>
     <row r="53" ht="16.5" customHeight="1"/>

--- a/관리/WBS(작업분할구조도)_v1.xlsx
+++ b/관리/WBS(작업분할구조도)_v1.xlsx
@@ -2089,3320 +2089,3850 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="6" customHeight="1"/>
-    <row r="5" spans="1:19" ht="31.5" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
+    <row r="5" spans="1:19" ht="18" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 기획 및 개발환경 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="18" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항 분석 / 기술 결정</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.1</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과제 지시서 분석 및 요구사항 도출</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요구사항 체크리스트</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.2</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 도메인 / 카테고리 값 정의</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회의 결정사항</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카테고리 6종 확정 (계약·약관 명칭 변경은 미결정)</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="4">
-        <v>2</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.3</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 추출 전략 수립 (레이어 우선 + OCR)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">카테고리 6종 확정 (계약·약관 명칭 변경은 미결정)</t>
-        </is>
-      </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기술 검토서</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.4</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진 선정 — PaddleOCR v5 확정</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Docker 동작 검증</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">컨테이너 실행 테스트 완료</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1">
-      <c r="A11" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.5</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 선정 — PostgreSQL (본프로젝트까지 단일 사용)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 교체 없이 연속 사용</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1">
-      <c r="A12" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B12" s="5"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1.6</t>
+        </is>
+      </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">샘플 문서 수집 (카테고리별)</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80%</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 문서</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회의록·공지사항·보고서·계약서·메뉴얼 확보. 기타 1건 미확보</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:19" ht="18" customHeight="1">
-      <c r="A13" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 계획</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:19" ht="18" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" s="4">
-        <v>1</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2.1</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">역할 분담 확정 (A 최재정 / B 박세현 / C 김보현)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">역할표</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:19" ht="18" customHeight="1">
-      <c r="A15" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H15" s="4">
-        <v>7</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2.2</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WBS 작성 / 갱신</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-06</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">90%</t>
         </is>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>256</v>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WBS</t>
+        </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">이슈 37건 · 결정사항 29건 반영. 최종 정리 남음</t>
         </is>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="4"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1">
-      <c r="A16" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="4">
-        <v>1</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2.3</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 브랜치 전략 / 공유파일 규칙 합의</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협업 규칙</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feature/기능명 (기능 단위)</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:19" ht="18" customHeight="1">
-      <c r="A17" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="4">
-        <v>1</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.2.4</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주말 작업 가능 여부 확인 — 가능 확정</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일정 확정</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시나리오 A 적용</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:19" ht="18" customHeight="1">
-      <c r="A18" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설계</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="4">
-        <v>1</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3.1</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 엔드포인트 6종 합의 완료</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 계약서</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경로/필드명(snake_case)/status 확정</t>
+        </is>
+      </c>
     </row>
     <row r="20" spans="1:19" ht="18" customHeight="1">
-      <c r="A20" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="4">
-        <v>2</v>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3.2</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 모델 설계 및 ERD 작성</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J20" s="5" t="s">
-        <v>283</v>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERD.png</t>
+        </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">ERD.png 업로드 완료</t>
         </is>
       </c>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-      <c r="S20" s="4"/>
     </row>
     <row r="21" spans="1:19" ht="18" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="4">
-        <v>2</v>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3.3</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면 정의서 작성</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">90%</t>
         </is>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>288</v>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면_정의서.pdf</t>
+        </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5화면 · 캡처 7장 · 흐름도 완료. PDF 저장 남음</t>
         </is>
       </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
     </row>
     <row r="22" spans="1:19" ht="18" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개발환경 구축</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:19" ht="18" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H23" s="4">
-        <v>1</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.1</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git / Docker 설치 (전원)</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">설치 확인</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="1:19" ht="18" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" s="4">
-        <v>1</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.2</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker-compose 구성 (db + api + frontend)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker-compose.yml</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck, env_file 포함</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:19" ht="18" customHeight="1">
-      <c r="A25" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" s="4">
-        <v>1</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.3</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공통 인프라 core/ 구현</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config/예외/로깅/미들웨어/트랜잭션</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:19" ht="18" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-      <c r="S26" s="4"/>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.9</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 마일스톤: 전원 compose up + /health 200</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동작 확인</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미달 시 D2 블로킹</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:19" ht="18" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.10</t>
+        </is>
+      </c>
       <c r="C27" s="5"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="4"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드 프로젝트 초기 구성 (Vite + React)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend/ 구조</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:19" ht="18" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B28" s="5"/>
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.11</t>
+        </is>
+      </c>
       <c r="C28" s="5"/>
-      <c r="D28" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28" s="4">
-        <v>1</v>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="L28" s="20"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-      <c r="S28" s="4"/>
-    </row>
-    <row r="29" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt 의존성 정리 및 중복 제거</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-004 · ISS-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="18" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4.12</t>
+        </is>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">개인 실행 환경 분리 (compose override)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker-compose.override.yml</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-031 · ISS-032. 결정사항 26</t>
+        </is>
+      </c>
     </row>
     <row r="30" spans="1:19" ht="18" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 / 텍스트 추출  [A · 재정]</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:19" ht="18" customHeight="1">
-      <c r="A31" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G31" s="11">
-        <v>46235</v>
-      </c>
-      <c r="H31" s="4">
-        <v>1</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
     </row>
     <row r="32" spans="1:19" ht="18" customHeight="1">
-      <c r="A32" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H32" s="4">
-        <v>2</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.1</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">upload_router.py — POST /api/documents</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46235</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 API</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동기 라우터</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:19" ht="18" customHeight="1">
-      <c r="A33" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H33" s="12">
-        <v>2</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.2</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extraction_service.py — 업로드/추출 로직</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서비스</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repository 경유</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:19" ht="18" customHeight="1">
-      <c r="A34" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F34" s="11">
-        <v>46236</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H34" s="4">
-        <v>2</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J34" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.3</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py (PyMuPDF)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PdfExtractor</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주 경로</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="1:19" ht="18" customHeight="1">
-      <c r="A35" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F35" s="11">
-        <v>46236</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H35" s="12">
-        <v>2</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J35" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.4</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 검증 (10MB / 30p / 확장자)</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증 로직</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">registry.get()이 확장자 검증</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="1:19" ht="18" customHeight="1">
-      <c r="A36" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="11">
-        <v>46234</v>
-      </c>
-      <c r="G36" s="11">
-        <v>46234</v>
-      </c>
-      <c r="H36" s="4">
-        <v>1</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.5</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docx / hwpx extractor</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현체 2종</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구형 HWP 제외</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:19" ht="18" customHeight="1">
-      <c r="A37" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F37" s="11">
-        <v>46234</v>
-      </c>
-      <c r="G37" s="11">
-        <v>46234</v>
-      </c>
-      <c r="H37" s="12">
-        <v>1</v>
-      </c>
-      <c r="I37" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="L37" s="10"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.6</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements OCR 주석 해제 + 전원 재빌드 공지</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 사전 공지 필수</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="1:19" ht="18" customHeight="1">
-      <c r="A38" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H38" s="12">
-        <v>3</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.7</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_extractor.py (PaddleOCR) + 이미지 크기 측정</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OcrExtractor, 이미지 크기</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배포 용량 확인용</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1">
-      <c r="A39" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F39" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H39" s="12">
-        <v>1</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J39" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="K39" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.8</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extractor registry 등록 (dependencies.py)</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레지스트리 등록</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공유파일 — 즉시 푸시</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="1:19" ht="18" customHeight="1">
-      <c r="A40" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H40" s="12">
-        <v>1</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J40" s="22" t="s">
-        <v>348</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.9</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 보안 강화 (UUID 파일 저장 + 경로 조작 방지)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J40" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extraction_service.py</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
+        </is>
+      </c>
     </row>
     <row r="41" spans="1:19" ht="18" customHeight="1">
-      <c r="A41" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B41" s="5"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.9</t>
+        </is>
+      </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F41" s="11">
-        <v>46236</v>
-      </c>
-      <c r="G41" s="11">
-        <v>46236</v>
-      </c>
-      <c r="H41" s="12">
-        <v>1</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J41" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 보안 강화 (UUID 저장 + 경로 조작 방지)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extraction_service.py</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1">
-      <c r="A42" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F42" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H42" s="12">
-        <v>1</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="K42" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.10</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 텍스트 + 이미지 OCR 통합 추출 (좌표 기반 병합)</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J42" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py, layout.py</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 픽셀→PDF 좌표 변환. ExtractMethod.HYBRID</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="1:19" ht="18" customHeight="1">
-      <c r="A43" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B43" s="5"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.10</t>
+        </is>
+      </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H43" s="12">
-        <v>1</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF 텍스트 + 이미지 OCR 통합 추출 (좌표 병합)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py · layout.py</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 픽셀 → PDF 좌표 변환. ExtractMethod.HYBRID 산출</t>
+        </is>
+      </c>
     </row>
     <row r="44" spans="1:19" ht="18" customHeight="1">
-      <c r="A44" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H44" s="12">
-        <v>1</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="K44" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="4"/>
-      <c r="S44" s="4"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.11</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동시 요청 시 OCR 엔진 충돌 방지</t>
+        </is>
+      </c>
     </row>
     <row r="45" spans="1:19" ht="18" customHeight="1">
-      <c r="A45" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.11</t>
+        </is>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동시 요청 시 엔진 충돌 방지</t>
+        </is>
+      </c>
     </row>
     <row r="46" spans="1:19" ht="18" customHeight="1">
-      <c r="A46" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H46" s="4">
-        <v>2</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J46" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="K46" s="5"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4"/>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.12</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외 처리</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 결과 실패 처리, HWPX 내부 이미지 오류는 해당 이미지만 건너뜀</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:19" ht="18" customHeight="1">
-      <c r="A47" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="B47" s="5"/>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.12</t>
+        </is>
+      </c>
       <c r="C47" s="5"/>
-      <c r="D47" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H47" s="4">
-        <v>1</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J47" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="K47" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-    </row>
-    <row r="48" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A48" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외 처리</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빈 결과 실패 처리. HWPX 내부 이미지 오류는 건너뜀</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="18" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.13</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS=45,000)</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config.py, extractor</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-009 / 결정사항 12</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:19" ht="18" customHeight="1">
-      <c r="A49" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.13</t>
+        </is>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config.py · extractor</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-010 · 결정사항 12</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:19" ht="18" customHeight="1">
-      <c r="A50" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F50" s="11">
-        <v>46234</v>
-      </c>
-      <c r="G50" s="11">
-        <v>46234</v>
-      </c>
-      <c r="H50" s="12">
-        <v>1</v>
-      </c>
-      <c r="I50" s="18">
-        <v>1</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="K50" s="5"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.14</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증 로직, error_codes</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일 크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:19" ht="18" customHeight="1">
-      <c r="A51" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="B51" s="5"/>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.14</t>
+        </is>
+      </c>
       <c r="C51" s="5"/>
-      <c r="D51" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F51" s="11">
-        <v>46234</v>
-      </c>
-      <c r="G51" s="11">
-        <v>46234</v>
-      </c>
-      <c r="H51" s="12">
-        <v>1</v>
-      </c>
-      <c r="I51" s="18">
-        <v>1</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="K51" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="L51" s="4"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증 로직 · error_codes</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
+        </is>
+      </c>
     </row>
     <row r="52" spans="1:19" ht="18" customHeight="1">
-      <c r="A52" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="B52" s="5"/>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.15</t>
+        </is>
+      </c>
       <c r="C52" s="5"/>
-      <c r="D52" s="8" t="s">
-        <v>386</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H52" s="12">
-        <v>2</v>
-      </c>
-      <c r="I52" s="18">
-        <v>1</v>
-      </c>
-      <c r="J52" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="L52" s="4"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesseract 추출기 구현</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tesseract_extractor.py</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국어·영어 학습 데이터. Dockerfile apt 패키지 추가</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:19" ht="18" customHeight="1">
-      <c r="A53" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="B53" s="5"/>
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.16</t>
+        </is>
+      </c>
       <c r="C53" s="5"/>
-      <c r="D53" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E53" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H53" s="4">
-        <v>2</v>
-      </c>
-      <c r="I53" s="18">
-        <v>1</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="K53" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="L53" s="4"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진 비교 API</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_compare_router · service</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 1 근거 확보용</t>
+        </is>
+      </c>
     </row>
     <row r="54" spans="1:19" ht="18" customHeight="1">
-      <c r="A54" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="B54" s="5"/>
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.17</t>
+        </is>
+      </c>
       <c r="C54" s="5"/>
-      <c r="D54" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H54" s="12">
-        <v>2</v>
-      </c>
-      <c r="I54" s="18">
-        <v>1</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="L54" s="4"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 추출기 추가 및 비교 대상 확장</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">easyocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 6종으로 확장. CPU 전용 torch 고정 (ISS-030)</t>
+        </is>
+      </c>
     </row>
     <row r="55" spans="1:19" ht="18" customHeight="1">
-      <c r="A55" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="B55" s="5"/>
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.18</t>
+        </is>
+      </c>
       <c r="C55" s="5"/>
-      <c r="D55" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H55" s="12">
-        <v>1</v>
-      </c>
-      <c r="I55" s="18">
-        <v>1</v>
-      </c>
-      <c r="J55" s="22" t="s">
-        <v>397</v>
-      </c>
-      <c r="K55" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 레이어 같은 줄 병합</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-020. 줄 단위 요소화 후 병합</t>
+        </is>
+      </c>
     </row>
     <row r="56" spans="1:19" ht="18" customHeight="1">
-      <c r="A56" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="B56" s="5"/>
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.19</t>
+        </is>
+      </c>
       <c r="C56" s="5"/>
-      <c r="D56" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="E56" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H56" s="12">
-        <v>1</v>
-      </c>
-      <c r="I56" s="18">
-        <v>1</v>
-      </c>
-      <c r="J56" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>402</v>
-      </c>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 정확도 측정 방식 개선 (정답 데이터 기반)</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_ground_truth.py</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">편집거리 기반. 결정사항 24</t>
+        </is>
+      </c>
     </row>
     <row r="57" spans="1:19" ht="18" customHeight="1">
-      <c r="A57" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="B57" s="5"/>
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.20</t>
+        </is>
+      </c>
       <c r="C57" s="5"/>
-      <c r="D57" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H57" s="4">
-        <v>1</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 입력 형식 확장 (문서 → 이미지 변환)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_compare_image_loader.py</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 25</t>
+        </is>
+      </c>
     </row>
     <row r="58" spans="1:19" ht="18" customHeight="1">
-      <c r="A58" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="B58" s="5"/>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.21</t>
+        </is>
+      </c>
       <c r="C58" s="5"/>
-      <c r="D58" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H58" s="4">
-        <v>2</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 품질 분석 기반 전처리 동적 선택</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preprocessing.py · ocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">품질 측정 후 필요한 단계만 적용. 처리 시간 3배 증가 (ISS-036)</t>
+        </is>
+      </c>
     </row>
     <row r="59" spans="1:19" ht="18" customHeight="1">
-      <c r="A59" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
-      <c r="N59" s="7"/>
-      <c r="O59" s="7"/>
-      <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
-      <c r="R59" s="7"/>
-      <c r="S59" s="7"/>
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.22</t>
+        </is>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하이브리드 PDF 읽기 순서 처리</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reading_order.py</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다단 문서 순서 복원. 표 영역 오인식 수정</t>
+        </is>
+      </c>
     </row>
     <row r="60" spans="1:19" ht="18" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="B60" s="5"/>
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1.23</t>
+        </is>
+      </c>
       <c r="C60" s="5"/>
-      <c r="D60" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F60" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G60" s="11">
-        <v>46237</v>
-      </c>
-      <c r="H60" s="4">
-        <v>1</v>
-      </c>
-      <c r="I60" s="18">
-        <v>1</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="K60" s="5"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EasyOCR 메모리 격리 (별도 프로세스)</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">easyocr_subprocess_extractor.py · workers/</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-035. 호출 종료 시 메모리 완전 회수</t>
+        </is>
+      </c>
     </row>
     <row r="61" spans="1:19" ht="18" customHeight="1">
-      <c r="A61" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="E61" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="F61" s="11">
-        <v>46237</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H61" s="12">
-        <v>1</v>
-      </c>
-      <c r="I61" s="18">
-        <v>1</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="K61" s="5"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-    </row>
-    <row r="62" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A62" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="18" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.1</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면 + 드래그앤드롭</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UploadPage</t>
+        </is>
+      </c>
     </row>
     <row r="63" spans="1:19" ht="18" customHeight="1">
-      <c r="A63" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
-      <c r="N63" s="7"/>
-      <c r="O63" s="7"/>
-      <c r="P63" s="7"/>
-      <c r="Q63" s="7"/>
-      <c r="R63" s="7"/>
-      <c r="S63" s="7"/>
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로딩 상태 UI (status 단계 표시)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spinner/StatusBar</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지시서 필수항목</t>
+        </is>
+      </c>
     </row>
     <row r="64" spans="1:19" ht="18" customHeight="1">
-      <c r="A64" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="B64" s="5"/>
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.3</t>
+        </is>
+      </c>
       <c r="C64" s="5"/>
-      <c r="D64" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H64" s="4">
-        <v>2</v>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">원본 미리보기 + 추출 텍스트 비교 화면</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J64" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="K64" s="5"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본프로젝트 '영역별 수정' 기능의 읽기 전용 선행 구현</t>
+        </is>
+      </c>
     </row>
     <row r="65" spans="1:19" ht="18" customHeight="1">
-      <c r="A65" s="4" t="s">
-        <v>421</v>
-      </c>
-      <c r="B65" s="5"/>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.4</t>
+        </is>
+      </c>
       <c r="C65" s="5"/>
-      <c r="D65" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H65" s="4">
-        <v>1</v>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면 재구성 (드롭존 + 3단계 진행)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J65" s="5" t="s">
-        <v>423</v>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면</t>
+        </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">목업 안3 반영. 공통 컴포넌트 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="18" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.5</t>
+        </is>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 화면</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OcrComparePage</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ocr-compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="18" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 분석 — 요약 / 카테고리  [B · 세현]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="18" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="18" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.1</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prompts.py — 프롬프트 + PROMPT_VERSION</t>
+        </is>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프롬프트 설계</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="18" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.2</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">summary_analyzer.py (async)</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G70" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SummaryAnalyzer</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generate_with_meta 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="18" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.3</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category_analyzer.py (Literal로 값 고정)</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CategoryAnalyzer</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">값 고정 안 하면 C 필터 깨짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="18" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.4</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis_service.py + analysis_router.py (async)</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석 API</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재분석 시 행 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="18" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.5</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyzer registry 등록 (dependencies.py)</t>
+        </is>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레지스트리 등록</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공유파일 — 즉시 푸시</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="18" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.6</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J74" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">openai_client.py</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구현 완료.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="18" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.7</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage.jsx</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/B/C 파트 진입 구성</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="18" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.8</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토큰/지연/모델명 기록 검증</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyses 컬럼 확인</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 본프로젝트 필수 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="18" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.8</t>
+        </is>
+      </c>
+      <c r="C77" s="5"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">openai_client.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="18" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.9</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 실연동 전환 (계정 확보 후)</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">openai_client.py</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그전까지 FakeClient</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="18" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.9</t>
+        </is>
+      </c>
+      <c r="C79" s="5"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약·분류 병렬 실행 최적화</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis_service.py</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-018. asyncio.gather 로 응답 시간 단축</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="18" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.10</t>
+        </is>
+      </c>
+      <c r="C80" s="5"/>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 실연동 전환 (FAKE → 실제 호출)</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.env · compose override</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-031 해결 후 전환. 요약·분류·근거 정상 생성 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="18" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="18" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2.1</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석 요청 / 진행 표시</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G82" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyze 연동</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="18" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2.2</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약 / 카테고리 결과 컴포넌트</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ResultView</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="18" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2.3</t>
+        </is>
+      </c>
+      <c r="C84" s="5"/>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="18" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조회 / 검색 / 출력  [C · 보현]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="18" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="18" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.1</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">document_service.py</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서비스</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="18" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.2</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">document_router.py — 목록/상세 (동기)</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조회 API</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">PageResponse 사용</t>
         </is>
       </c>
-      <c r="L65" s="4"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-    </row>
-    <row r="66" spans="1:19" ht="18" customHeight="1">
-      <c r="A66" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H66" s="4">
-        <v>1</v>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
+    </row>
+    <row r="89" spans="1:19" ht="18" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.3</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 (q / document_type / category)</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J66" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 API</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">파일명 + 본문 부분검색. 공백 정규화 포함 (ISS-034)</t>
         </is>
       </c>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-    </row>
-    <row r="67" spans="1:19" ht="18" customHeight="1">
-      <c r="A67" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H67" s="4">
-        <v>1</v>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
+    </row>
+    <row r="90" spans="1:19" ht="18" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.4</t>
+        </is>
+      </c>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다운로드 (.txt, 한글 파일명 대응)</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J67" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="K67" s="5" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다운로드 API</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">filename*=UTF-8''. 줄바꿈 버그 ISS-016 수정</t>
         </is>
       </c>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-    </row>
-    <row r="68" spans="1:19" ht="18" customHeight="1">
-      <c r="A68" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H68" s="4">
-        <v>1</v>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
+    </row>
+    <row r="91" spans="1:19" ht="18" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.5</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 (cascade + 업로드 파일 제거)</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J68" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELETE API</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">결정사항 18 변경으로 구현. cascade + 업로드 파일 제거</t>
         </is>
       </c>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-    </row>
-    <row r="69" spans="1:19" ht="18" customHeight="1">
-      <c r="A69" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="7"/>
-      <c r="K69" s="7"/>
-      <c r="L69" s="7"/>
-      <c r="M69" s="7"/>
-      <c r="N69" s="7"/>
-      <c r="O69" s="7"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
-      <c r="R69" s="7"/>
-      <c r="S69" s="7"/>
-    </row>
-    <row r="70" spans="1:19" ht="18" customHeight="1">
-      <c r="A70" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H70" s="4">
-        <v>2</v>
-      </c>
-      <c r="I70" s="4" t="inlineStr">
+    </row>
+    <row r="92" spans="1:19" ht="18" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="18" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.1</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 화면</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J70" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ListPage</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">테이블 + 검색 + 페이징</t>
         </is>
       </c>
-      <c r="L70" s="4"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-    </row>
-    <row r="71" spans="1:19" ht="18" customHeight="1">
-      <c r="A71" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H71" s="4">
-        <v>1</v>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
+    </row>
+    <row r="94" spans="1:19" ht="18" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.2</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세 화면 (요약 + 카테고리)</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J71" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DetailPage</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">원문 접기·펼치기 + 분석 이력</t>
         </is>
       </c>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="10"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-    </row>
-    <row r="72" spans="1:19" ht="18" customHeight="1">
-      <c r="A72" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H72" s="4">
-        <v>1</v>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
+    </row>
+    <row r="95" spans="1:19" ht="18" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.3</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 UI + 다운로드 버튼</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J72" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="K72" s="5"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="10"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-    </row>
-    <row r="73" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A73" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="M73" s="6"/>
-      <c r="N73" s="6"/>
-      <c r="O73" s="6"/>
-      <c r="P73" s="6"/>
-      <c r="Q73" s="6"/>
-      <c r="R73" s="6"/>
-      <c r="S73" s="6"/>
-    </row>
-    <row r="74" spans="1:19" ht="18" customHeight="1">
-      <c r="A74" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-      <c r="H74" s="7"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="7"/>
-      <c r="K74" s="7"/>
-      <c r="L74" s="7"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="7"/>
-      <c r="O74" s="7"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
-      <c r="R74" s="7"/>
-      <c r="S74" s="7"/>
-    </row>
-    <row r="75" spans="1:19" ht="18" customHeight="1">
-      <c r="A75" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H75" s="4">
-        <v>1</v>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SearchBar</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="18" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.4</t>
+        </is>
+      </c>
+      <c r="C96" s="5"/>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공통 컴포넌트 + 디자인 토큰</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J75" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03 관통 확인</t>
-        </is>
-      </c>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="20"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-    </row>
-    <row r="76" spans="1:19" ht="18" customHeight="1">
-      <c r="A76" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="H76" s="4">
-        <v>2</v>
-      </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-016 · ISS-017</t>
-        </is>
-      </c>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="10"/>
-      <c r="O76" s="10"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-    </row>
-    <row r="77" spans="1:19" ht="18" customHeight="1">
-      <c r="A77" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="B77" s="7"/>
-      <c r="C77" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7"/>
-      <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
-      <c r="N77" s="7"/>
-      <c r="O77" s="7"/>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
-      <c r="R77" s="7"/>
-      <c r="S77" s="7"/>
-    </row>
-    <row r="78" spans="1:19" ht="18" customHeight="1">
-      <c r="A78" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H78" s="4">
-        <v>1</v>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66항목 전 항목 판정 완료</t>
-        </is>
-      </c>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="10"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-    </row>
-    <row r="79" spans="1:19" ht="18" customHeight="1">
-      <c r="A79" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H79" s="4">
-        <v>1</v>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80%</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건은 08-06 오전</t>
-        </is>
-      </c>
-      <c r="L79" s="4"/>
-      <c r="M79" s="4"/>
-      <c r="N79" s="4"/>
-      <c r="O79" s="4"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="4"/>
-      <c r="R79" s="4"/>
-      <c r="S79" s="4"/>
-    </row>
-    <row r="80" spans="1:19" ht="18" customHeight="1">
-      <c r="A80" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H80" s="4">
-        <v>2</v>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이슈관리 시트 46건 기록</t>
-        </is>
-      </c>
-      <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4"/>
-      <c r="O80" s="4"/>
-      <c r="P80" s="10"/>
-      <c r="Q80" s="10"/>
-      <c r="R80" s="4"/>
-      <c r="S80" s="4"/>
-    </row>
-    <row r="81" spans="1:19" ht="18" customHeight="1">
-      <c r="A81" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="7"/>
-      <c r="S81" s="7"/>
-    </row>
-    <row r="82" spans="1:19" ht="18" customHeight="1">
-      <c r="A82" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H82" s="4">
-        <v>2</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J82" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="K82" s="5"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="10"/>
-      <c r="Q82" s="10"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-    </row>
-    <row r="83" spans="1:19" ht="18" customHeight="1">
-      <c r="A83" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H83" s="4">
-        <v>1</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="K83" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="L83" s="4"/>
-      <c r="M83" s="4"/>
-      <c r="N83" s="4"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="4"/>
-      <c r="S83" s="4"/>
-    </row>
-    <row r="84" spans="1:19" ht="18" customHeight="1">
-      <c r="A84" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H84" s="4">
-        <v>1</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="K84" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-      <c r="Q84" s="10"/>
-      <c r="R84" s="4"/>
-      <c r="S84" s="4"/>
-    </row>
-    <row r="85" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-      <c r="M85" s="6"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="6"/>
-      <c r="Q85" s="6"/>
-      <c r="R85" s="6"/>
-      <c r="S85" s="6"/>
-    </row>
-    <row r="86" spans="1:19" ht="18" customHeight="1">
-      <c r="A86" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-      <c r="H86" s="7"/>
-      <c r="I86" s="7"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
-      <c r="N86" s="7"/>
-      <c r="O86" s="7"/>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="7"/>
-      <c r="R86" s="7"/>
-      <c r="S86" s="7"/>
-    </row>
-    <row r="87" spans="1:19" ht="18" customHeight="1">
-      <c r="A87" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H87" s="4">
-        <v>2</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J87" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="4"/>
-    </row>
-    <row r="88" spans="1:19" ht="18" customHeight="1">
-      <c r="A88" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H88" s="4">
-        <v>1</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="K88" s="5"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="10"/>
-      <c r="S88" s="4"/>
-    </row>
-    <row r="89" spans="1:19" ht="18" customHeight="1">
-      <c r="A89" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-      <c r="H89" s="7"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="7"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="7"/>
-    </row>
-    <row r="90" spans="1:19" ht="18" customHeight="1">
-      <c r="A90" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H90" s="4">
-        <v>1</v>
-      </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05 코드 프리즈. 이후 산출물 작업만 진행</t>
-        </is>
-      </c>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="20"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-    </row>
-    <row r="91" spans="1:19" ht="18" customHeight="1">
-      <c r="A91" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H91" s="4">
-        <v>2</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="K91" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="4"/>
-    </row>
-    <row r="92" spans="1:19" ht="18" customHeight="1">
-      <c r="A92" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H92" s="4">
-        <v>2</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="10"/>
-      <c r="R92" s="10"/>
-      <c r="S92" s="4"/>
-    </row>
-    <row r="93" spans="1:19" ht="18" customHeight="1">
-      <c r="A93" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H93" s="4">
-        <v>1</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="K93" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="4"/>
-    </row>
-    <row r="94" spans="1:19" ht="18" customHeight="1">
-      <c r="A94" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="19" t="s">
-        <v>504</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>505</v>
-      </c>
-      <c r="H94" s="4">
-        <v>1</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="20"/>
-    </row>
-    <row r="95" spans="1:19" ht="16.5" customHeight="1"/>
-    <row r="96" spans="1:19" ht="18" customHeight="1">
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추가 반영 (08-03 ~ 08-05) — 정렬 시 각 ID 위치로 이동</t>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tokens.css · Badge · Spinner · ErrorBanner</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 15</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:19" ht="18" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1.6</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기획</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.5</t>
+        </is>
+      </c>
+      <c r="C97" s="5"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">샘플 문서 수집 (카테고리별)</t>
+          <t xml:space="preserve">App.jsx 라우터 통합</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">80%</t>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">테스트 문서</t>
+          <t xml:space="preserve">App.jsx</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">회의록·공지사항·보고서·계약서·메뉴얼 확보. 기타 1건 미확보</t>
+          <t xml:space="preserve">ISS-028. useState 토글 → react-router</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:19" ht="18" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.10</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개발환경</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.6</t>
+        </is>
+      </c>
+      <c r="C98" s="5"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">프론트엔드 프로젝트 초기 구성 (Vite + React)</t>
+          <t xml:space="preserve">목록에 업로드 진입점 추가</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -5412,12 +5942,12 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">07-31</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">07-31</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -5432,39 +5962,40 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">frontend/ 구조</t>
+          <t xml:space="preserve">ListPage</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 19</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:19" ht="18" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.11</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개발환경</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.7</t>
+        </is>
+      </c>
+      <c r="C99" s="5"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements.txt 의존성 정리 및 중복 제거</t>
+          <t xml:space="preserve">목록 + 상세 패널 (마스터-디테일)</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">07-31</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">07-31</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -5479,29 +6010,25 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements.txt</t>
+          <t xml:space="preserve">ListPage</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-004 · ISS-008</t>
+          <t xml:space="preserve">결정사항 20. DocumentDetail 수정 없이 재사용</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:19" ht="18" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.12</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">개발환경</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.8</t>
+        </is>
+      </c>
+      <c r="C100" s="5"/>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">개인 실행 환경 분리 (compose override)</t>
+          <t xml:space="preserve">레이아웃 폭·여백 통일 및 헤더 정리</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -5511,12 +6038,12 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5531,44 +6058,40 @@
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker-compose.override.yml</t>
+          <t xml:space="preserve">tokens.css · MainLayout</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-031 · ISS-032. 결정사항 26</t>
+          <t xml:space="preserve">컨테이너 1440px. --c-page-x 변수화</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:19" ht="18" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.9</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.9</t>
+        </is>
+      </c>
+      <c r="C101" s="5"/>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 보안 강화 (UUID 저장 + 경로 조작 방지)</t>
+          <t xml:space="preserve">홈 화면 기능 설명 영역 구성</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -5583,44 +6106,40 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">extraction_service.py</t>
+          <t xml:space="preserve">MainPage</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
+          <t xml:space="preserve">기능 확장 시 안내서 역할. 운영 메뉴얼과 문구 공유</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:19" ht="18" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.10</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.10</t>
+        </is>
+      </c>
+      <c r="C102" s="5"/>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDF 텍스트 + 이미지 OCR 통합 추출 (좌표 병합)</t>
+          <t xml:space="preserve">검색 공백 정규화</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -5635,44 +6154,40 @@
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pdf_extractor.py · layout.py</t>
+          <t xml:space="preserve">document_repository.py</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지 픽셀 → PDF 좌표 변환. ExtractMethod.HYBRID 산출</t>
+          <t xml:space="preserve">ISS-034. 중복 구현 통합 (결정사항 28)</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:19" ht="18" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.11</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.11</t>
+        </is>
+      </c>
+      <c r="C103" s="5"/>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
+          <t xml:space="preserve">삭제 화면 (확인 창 · 목록 갱신)</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -5687,44 +6202,35 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_extractor.py</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동시 요청 시 엔진 충돌 방지</t>
+          <t xml:space="preserve">ListPage · DetailPage · DocumentDetail</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:19" ht="18" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.12</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4.2.12</t>
+        </is>
+      </c>
+      <c r="C104" s="5"/>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
+          <t xml:space="preserve">UI/UX 전면 개선 및 공통 컴포넌트 리팩터링</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -5739,44 +6245,44 @@
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">예외 처리</t>
+          <t xml:space="preserve">PageHeader · EmptyState · Icon · tokens.css</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 결과 실패 처리. HWPX 내부 이미지 오류는 건너뜀</t>
+          <t xml:space="preserve">반응형 구조 정리. 삭제 기능은 새 디자인 시스템으로 이식</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:19" ht="18" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.13</t>
+          <t xml:space="preserve">4.2.13</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">백엔드</t>
+          <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS)</t>
+          <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5791,148 +6297,63 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">config.py · extractor</t>
+          <t xml:space="preserve">NotFoundPage.jsx</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-010 · 결정사항 12</t>
+          <t xml:space="preserve">결정사항 27. 종전 빈 화면 개선</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:19" ht="18" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1.14</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D106" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검증 로직 · error_codes</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 / 테스트 / 배포</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:19" ht="18" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1.15</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D107" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tesseract 추출기 구현</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tesseract_extractor.py</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">한국어·영어 학습 데이터. Dockerfile apt 패키지 추가</t>
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:19" ht="18" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.16</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D108" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 엔진 비교 API</t>
+          <t xml:space="preserve">5.1.1</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 마일스톤: E2E 전 구간 관통</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -5947,49 +6368,44 @@
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_compare_router · service</t>
+          <t xml:space="preserve">동작 확인</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 1 근거 확보용</t>
+          <t xml:space="preserve">08-03 관통 확인</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:19" ht="18" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.17</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EasyOCR 추출기 추가 및 비교 대상 확장</t>
+          <t xml:space="preserve">5.1.2</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 계약 불일치 수정</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -5999,96 +6415,51 @@
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">easyocr_extractor.py</t>
+          <t xml:space="preserve">수정 이력</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지 6종으로 확장. CPU 전용 torch 고정 (ISS-030)</t>
+          <t xml:space="preserve">ISS-016 · ISS-017</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:19" ht="18" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1.18</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D110" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">텍스트 레이어 같은 줄 병합</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pdf_extractor.py</t>
-        </is>
-      </c>
-      <c r="K110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-020. 줄 단위 요소화 후 병합</t>
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:19" ht="18" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.19</t>
-        </is>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D111" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 정확도 측정 방식 개선 (정답 데이터 기반)</t>
+          <t xml:space="preserve">5.2.1</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위 테스트 작성 / 실행</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -6103,44 +6474,39 @@
       </c>
       <c r="J111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_ground_truth.py</t>
+          <t xml:space="preserve">단위테스트결과서.xlsx</t>
         </is>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">편집거리 기반. 결정사항 24</t>
+          <t xml:space="preserve">66항목 전 항목 판정 완료</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:19" ht="18" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.20</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D112" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 비교 입력 형식 확장 (문서 → 이미지 변환)</t>
+          <t xml:space="preserve">5.2.2</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 테스트 시나리오 작성 / 실행</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -6150,54 +6516,49 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">80%</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_compare_image_loader.py</t>
+          <t xml:space="preserve">통합테스트시나리오.xlsx</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 25</t>
+          <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건은 08-06 오전</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:19" ht="18" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.21</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D113" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이미지 품질 분석 기반 전처리 동적 선택</t>
+          <t xml:space="preserve">5.2.3</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 / 이슈 리포트 정리</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">08-05</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -6207,44 +6568,44 @@
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">preprocessing.py · ocr_extractor.py</t>
+          <t xml:space="preserve">이슈리포트</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">품질 측정 후 필요한 단계만 적용. 처리 시간 3배 증가 (ISS-036)</t>
+          <t xml:space="preserve">이슈관리 시트 46건 기록</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:19" ht="18" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.22</t>
+          <t xml:space="preserve">5.2.4</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">백엔드</t>
+          <t xml:space="preserve">테스트</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">하이브리드 PDF 읽기 순서 처리</t>
+          <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -6254,34 +6615,34 @@
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reading_order.py</t>
+          <t xml:space="preserve">SQL 로그 · 개선 전후 수치</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다단 문서 순서 복원. 표 영역 오인식 수정</t>
+          <t xml:space="preserve">결정사항 17. 본프로젝트 이관 검토</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:19" ht="18" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.23</t>
+          <t xml:space="preserve">5.2.5</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">백엔드</t>
+          <t xml:space="preserve">테스트</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EasyOCR 메모리 격리 (별도 프로세스)</t>
+          <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -6291,64 +6652,64 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">60%</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">easyocr_subprocess_extractor.py · workers/</t>
+          <t xml:space="preserve">비교 결과</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-035. 호출 종료 시 메모리 완전 회수</t>
+          <t xml:space="preserve">confidence 기반 측정 완료. 정답 데이터 기반 측정 남음</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:19" ht="18" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2.3</t>
+          <t xml:space="preserve">5.2.6</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">프론트엔드</t>
+          <t xml:space="preserve">테스트</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">원본 미리보기 + 추출 텍스트 비교 화면</t>
+          <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -6363,86 +6724,41 @@
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 화면</t>
+          <t xml:space="preserve">csv · xlsx</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">본프로젝트 '영역별 수정' 기능의 읽기 전용 선행 구현</t>
+          <t xml:space="preserve">ISS-037. UTF-8 통일 · 이슈 단일 표 재번호 (결정사항 29)</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:19" ht="18" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2.4</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 화면 재구성 (드롭존 + 3단계 진행)</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 화면</t>
-        </is>
-      </c>
-      <c r="K117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목업 안3 반영. 공통 컴포넌트 재사용</t>
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배포</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:19" ht="18" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2.5</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 비교 화면</t>
+          <t xml:space="preserve">5.3.1</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드 컨테이너 검증</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -6452,59 +6768,49 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OcrComparePage</t>
-        </is>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">/ocr-compare</t>
+          <t xml:space="preserve">frontend Dockerfile</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:19" ht="18" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.8</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
+          <t xml:space="preserve">5.3.2</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker compose 전체 3컨테이너 기동 검증</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -6514,44 +6820,44 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">openai_client.py</t>
+          <t xml:space="preserve">배포 확인</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PaddleOCR 포함 이미지</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:19" ht="18" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.9</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D120" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요약·분류 병렬 실행 최적화</t>
+          <t xml:space="preserve">5.3.3</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영 메뉴얼 / 배포 문서</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -6561,133 +6867,53 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">analysis_service.py</t>
+          <t xml:space="preserve">운영 메뉴얼</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-018. asyncio.gather 로 응답 시간 단축</t>
+          <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:19" ht="18" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1.10</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-      <c r="D121" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenAI 실연동 전환 (FAKE → 실제 호출)</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.env · compose override</t>
-        </is>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-031 해결 후 전환. 요약·분류·근거 정상 생성 확인</t>
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 / 발표 준비</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:19" ht="18" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.2.3</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D122" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MainPage.jsx</t>
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 산출물</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:19" ht="18" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.4</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D123" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공통 컴포넌트 + 디자인 토큰</t>
+          <t xml:space="preserve">6.1.1</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 완료 보고서</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -6697,64 +6923,59 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tokens.css · Badge · Spinner · ErrorBanner</t>
+          <t xml:space="preserve">완료 보고서</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 15</t>
+          <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:19" ht="18" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.5</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D124" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">App.jsx 라우터 통합</t>
+          <t xml:space="preserve">6.1.2</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 11종 최종 점검</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -6764,101 +6985,51 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">App.jsx</t>
-        </is>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-028. useState 토글 → react-router</t>
+          <t xml:space="preserve">제출 목록</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:19" ht="18" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2.6</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D125" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록에 업로드 진입점 추가</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ListPage</t>
-        </is>
-      </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항 19</t>
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:19" ht="18" customHeight="1">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.7</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D126" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 + 상세 패널 (마스터-디테일)</t>
+          <t xml:space="preserve">6.2.1</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 코드 프리즈</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -6873,148 +7044,133 @@
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ListPage</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 20. DocumentDetail 수정 없이 재사용</t>
+          <t xml:space="preserve">08-05 코드 프리즈. 이후 산출물 작업만 진행</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:19" ht="18" customHeight="1">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.8</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D127" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">레이아웃 폭·여백 통일 및 헤더 정리</t>
+          <t xml:space="preserve">6.2.2</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표자료(PPT) 작성 — 목차 5장</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tokens.css · MainLayout</t>
+          <t xml:space="preserve">발표자료.pptx</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">컨테이너 1440px. --c-page-x 변수화</t>
+          <t xml:space="preserve">전원 분담</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:19" ht="18" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.9</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D128" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">홈 화면 기능 설명 영역 구성</t>
+          <t xml:space="preserve">6.2.3</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표영상 녹화 / 편집</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I128" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MainPage</t>
+          <t xml:space="preserve">발표영상.zip</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">기능 확장 시 안내서 역할. 운영 메뉴얼과 문구 공유</t>
+          <t xml:space="preserve">시나리오 사전 작성</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:19" ht="18" customHeight="1">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.10</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D129" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 공백 정규화</t>
+          <t xml:space="preserve">6.2.4</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표 리허설 2회 (시간 측정)</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -7024,49 +7180,44 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">document_repository.py</t>
+          <t xml:space="preserve">리허설 기록</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-034. 중복 구현 통합 (결정사항 28)</t>
+          <t xml:space="preserve">전원 발표 필수</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:19" ht="18" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.11</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삭제 화면 (확인 창 · 목록 갱신)</t>
+          <t xml:space="preserve">6.2.5</t>
+        </is>
+      </c>
+      <c r="D130" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 최종 발표</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-07</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-07</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -7076,64 +7227,122 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ListPage · DetailPage · DocumentDetail</t>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팀원 전원 참여</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:19" ht="18" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2.12</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D131" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI/UX 전면 개선 및 공통 컴포넌트 리팩터링</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J131" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PageHeader · EmptyState · Icon · tokens.css</t>
-        </is>
-      </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반응형 구조 정리. 삭제 기능은 새 디자인 시스템으로 이식</t>
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WBS ID</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대분류</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중분류</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작업명</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">담당</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시작일</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">종료일</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일수</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행률</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7/31
+(금)</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1
+(토)</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/2
+(일)</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/3
+(월)</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/4
+(화)</t>
+        </is>
+      </c>
+      <c r="Q131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/5
+(수)</t>
+        </is>
+      </c>
+      <c r="R131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/6
+(목)</t>
+        </is>
+      </c>
+      <c r="S131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/7
+(금)</t>
         </is>
       </c>
     </row>
@@ -7143,11 +7352,7 @@
           <t xml:space="preserve">4.2.13</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
+      <c r="C132" s="5"/>
       <c r="D132" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
@@ -7195,11 +7400,7 @@
           <t xml:space="preserve">5.2.4</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
-        </is>
-      </c>
+      <c r="C133" s="5"/>
       <c r="D133" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
@@ -7247,11 +7448,7 @@
           <t xml:space="preserve">5.2.5</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
-        </is>
-      </c>
+      <c r="C134" s="5"/>
       <c r="D134" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
@@ -7299,11 +7496,7 @@
           <t xml:space="preserve">5.2.6</t>
         </is>
       </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
-        </is>
-      </c>
+      <c r="C135" s="5"/>
       <c r="D135" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>

--- a/관리/WBS(작업분할구조도)_v1.xlsx
+++ b/관리/WBS(작업분할구조도)_v1.xlsx
@@ -2089,84 +2089,101 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="6" customHeight="1"/>
-    <row r="5" spans="1:19" ht="18" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" spans="1:19" ht="31.5" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="18" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">프로젝트 기획 및 개발환경 구축</t>
         </is>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="18" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="7" spans="1:19" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">1.1</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">요구사항 분석 / 기술 결정</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="18" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.1.1</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">과제 지시서 분석 및 요구사항 도출</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요구사항 체크리스트</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1.2</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 도메인 / 카테고리 값 정의</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+          <t xml:space="preserve">1.1.1</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">과제 지시서 분석 및 요구사항 도출</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">전원</t>
         </is>
@@ -2178,44 +2195,39 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">07-31</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">회의 결정사항</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">카테고리 6종 확정 (계약·약관 명칭 변경은 미결정)</t>
+          <t xml:space="preserve">요구사항 체크리스트</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1.3</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">텍스트 추출 전략 수립 (레이어 우선 + OCR)</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">1.1.2</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 도메인 / 카테고리 값 정의</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2225,39 +2237,44 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">07-31</t>
+          <t xml:space="preserve">08-01</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">기술 검토서</t>
+          <t xml:space="preserve">회의 결정사항</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카테고리 6종 확정 (계약·약관 명칭 변경은 미결정)</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1.4</t>
+          <t xml:space="preserve">1.1.3</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 엔진 선정 — PaddleOCR v5 확정</t>
+          <t xml:space="preserve">텍스트 추출 전략 수립 (레이어 우선 + OCR)</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -2282,29 +2299,24 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Docker 동작 검증</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">컨테이너 실행 테스트 완료</t>
+          <t xml:space="preserve">기술 검토서</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1.5</t>
+          <t xml:space="preserve">1.1.4</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DB 선정 — PostgreSQL (본프로젝트까지 단일 사용)</t>
+          <t xml:space="preserve">OCR 엔진 선정 — PaddleOCR v5 확정</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2329,129 +2341,133 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항</t>
+          <t xml:space="preserve">Docker 동작 검증</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DB 교체 없이 연속 사용</t>
+          <t xml:space="preserve">컨테이너 실행 테스트 완료</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.1.5</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 선정 — PostgreSQL (본프로젝트까지 단일 사용)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 교체 없이 연속 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.1.6</t>
         </is>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">샘플 문서 수집 (카테고리별)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">전원</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-03</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-05</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">80%</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">테스트 문서</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">회의록·공지사항·보고서·계약서·메뉴얼 확보. 기타 1건 미확보</t>
         </is>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14" spans="1:19" ht="18" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">1.2</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">프로젝트 계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="18" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.2.1</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">역할 분담 확정 (A 최재정 / B 박세현 / C 김보현)</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">역할표</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:19" ht="18" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2.2</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WBS 작성 / 갱신</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+          <t xml:space="preserve">1.2.1</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">역할 분담 확정 (A 최재정 / B 박세현 / C 김보현)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">김보현</t>
         </is>
@@ -2463,44 +2479,39 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-06</t>
+          <t xml:space="preserve">07-31</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90%</t>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WBS</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이슈 37건 · 결정사항 29건 반영. 최종 정리 남음</t>
+          <t xml:space="preserve">역할표</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.2.3</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Git 브랜치 전략 / 공유파일 규칙 합의</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">1.2.2</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WBS 작성 / 갱신</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2510,150 +2521,150 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">07-31</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90%</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">협업 규칙</t>
+          <t xml:space="preserve">WBS</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">feature/기능명 (기능 단위)</t>
+          <t xml:space="preserve">이슈 37건 · 결정사항 29건 반영. 최종 정리 남음</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:19" ht="18" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.2.3</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git 브랜치 전략 / 공유파일 규칙 합의</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">협업 규칙</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">feature/기능명 (기능 단위)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="18" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.2.4</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">주말 작업 가능 여부 확인 — 가능 확정</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">김보현</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">07-31</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">07-31</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">일정 확정</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">시나리오 A 적용</t>
         </is>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" spans="1:19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">1.3</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">설계</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3.1</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 엔드포인트 6종 합의 완료</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 계약서</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경로/필드명(snake_case)/status 확정</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:19" ht="18" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3.2</t>
+          <t xml:space="preserve">1.3.1</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DB 모델 설계 및 ERD 작성</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">API 엔드포인트 6종 합의 완료</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2663,145 +2674,150 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">07-31</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERD.png</t>
+          <t xml:space="preserve">API 계약서</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERD.png 업로드 완료</t>
+          <t xml:space="preserve">경로/필드명(snake_case)/status 확정</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:19" ht="18" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.3.2</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DB 모델 설계 및 ERD 작성</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERD.png</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERD.png 업로드 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="18" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.3.3</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">화면 정의서 작성</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">김보현</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">07-31</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-01</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">90%</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">화면_정의서.pdf</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">5화면 · 캡처 7장 · 흐름도 완료. PDF 저장 남음</t>
         </is>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23" spans="1:19" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">1.4</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">개발환경 구축</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="18" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4.1</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Git / Docker 설치 (전원)</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07-31</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">설치 확인</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:19" ht="18" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.2</t>
+          <t xml:space="preserve">1.4.1</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker-compose 구성 (db + api + frontend)</t>
+          <t xml:space="preserve">Git / Docker 설치 (전원)</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2826,24 +2842,19 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker-compose.yml</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">healthcheck, env_file 포함</t>
+          <t xml:space="preserve">설치 확인</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:19" ht="18" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.3</t>
+          <t xml:space="preserve">1.4.2</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통 인프라 core/ 구현</t>
+          <t xml:space="preserve">docker-compose 구성 (db + api + frontend)</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2873,24 +2884,29 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">config/예외/로깅/미들웨어/트랜잭션</t>
+          <t xml:space="preserve">docker-compose.yml</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">healthcheck, env_file 포함</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:19" ht="18" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.9</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">★ 마일스톤: 전원 compose up + /health 200</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">1.4.3</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공통 인프라 core/ 구현</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2908,32 +2924,31 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작 확인</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미달 시 D2 블로킹</t>
+          <t xml:space="preserve">config/예외/로깅/미들웨어/트랜잭션</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:19" ht="18" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.10</t>
-        </is>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드 프로젝트 초기 구성 (Vite + React)</t>
+          <t xml:space="preserve">1.4.9</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 마일스톤: 전원 compose up + /health 200</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2951,32 +2966,31 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">frontend/ 구조</t>
+          <t xml:space="preserve">동작 확인</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미달 시 D2 블로킹</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:19" ht="18" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4.11</t>
-        </is>
-      </c>
-      <c r="C28" s="5"/>
+          <t xml:space="preserve">1.4.10</t>
+        </is>
+      </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements.txt 의존성 정리 및 중복 제거</t>
+          <t xml:space="preserve">프론트엔드 프로젝트 초기 구성 (Vite + React)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -3001,143 +3015,137 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements.txt</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-004 · ISS-008</t>
+          <t xml:space="preserve">frontend/ 구조</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:19" ht="18" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1.4.11</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt 의존성 정리 및 중복 제거</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07-31</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requirements.txt</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-004 · ISS-008</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="18" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">1.4.12</t>
         </is>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">개인 실행 환경 분리 (compose override)</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">김보현</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-05</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-05</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">docker-compose.override.yml</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">ISS-031 · ISS-032. 결정사항 26</t>
         </is>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="31" spans="1:19" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">업로드 / 텍스트 추출  [A · 재정]</t>
         </is>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="18" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="32" spans="1:19" ht="18" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">2.1</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">백엔드</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="18" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1.1</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">upload_router.py — POST /api/documents</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-01</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46235</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 API</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동기 라우터</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:19" ht="18" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.2</t>
+          <t xml:space="preserve">2.1.1</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">extraction_service.py — 업로드/추출 로직</t>
+          <t xml:space="preserve">upload_router.py — POST /api/documents</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3150,14 +3158,14 @@
           <t xml:space="preserve">08-01</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-02</t>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46235</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -3167,24 +3175,24 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">서비스</t>
+          <t xml:space="preserve">업로드 API</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repository 경유</t>
+          <t xml:space="preserve">동기 라우터</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:19" ht="18" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.3</t>
+          <t xml:space="preserve">2.1.2</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pdf_extractor.py (PyMuPDF)</t>
+          <t xml:space="preserve">extraction_service.py — 업로드/추출 로직</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -3199,10 +3207,10 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
@@ -3214,24 +3222,24 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PdfExtractor</t>
+          <t xml:space="preserve">서비스</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">주 경로</t>
+          <t xml:space="preserve">Repository 경유</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:19" ht="18" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.4</t>
+          <t xml:space="preserve">2.1.3</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">파일 검증 (10MB / 30p / 확장자)</t>
+          <t xml:space="preserve">pdf_extractor.py (PyMuPDF)</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3239,17 +3247,17 @@
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46236</t>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
@@ -3261,24 +3269,24 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">검증 로직</t>
+          <t xml:space="preserve">PdfExtractor</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">registry.get()이 확장자 검증</t>
+          <t xml:space="preserve">주 경로</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:19" ht="18" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.5</t>
+          <t xml:space="preserve">2.1.4</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">docx / hwpx extractor</t>
+          <t xml:space="preserve">파일 검증 (10MB / 30p / 확장자)</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3296,7 +3304,7 @@
           <t xml:space="preserve">08-03</t>
         </is>
       </c>
-      <c r="H36" s="12" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
@@ -3308,24 +3316,24 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">구현체 2종</t>
+          <t xml:space="preserve">검증 로직</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">구형 HWP 제외</t>
+          <t xml:space="preserve">registry.get()이 확장자 검증</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:19" ht="18" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.6</t>
+          <t xml:space="preserve">2.1.5</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements OCR 주석 해제 + 전원 재빌드 공지</t>
+          <t xml:space="preserve">docx / hwpx extractor</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3335,17 +3343,17 @@
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">46234</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46234</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -3355,24 +3363,24 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">requirements.txt</t>
+          <t xml:space="preserve">구현체 2종</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">★ 사전 공지 필수</t>
+          <t xml:space="preserve">구형 HWP 제외</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:19" ht="18" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.7</t>
+          <t xml:space="preserve">2.1.6</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_extractor.py (PaddleOCR) + 이미지 크기 측정</t>
+          <t xml:space="preserve">requirements OCR 주석 해제 + 전원 재빌드 공지</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3390,7 +3398,7 @@
           <t xml:space="preserve">46234</t>
         </is>
       </c>
-      <c r="H38" s="12" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
@@ -3402,24 +3410,24 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OcrExtractor, 이미지 크기</t>
+          <t xml:space="preserve">requirements.txt</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">배포 용량 확인용</t>
+          <t xml:space="preserve">★ 사전 공지 필수</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.8</t>
+          <t xml:space="preserve">2.1.7</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">extractor registry 등록 (dependencies.py)</t>
+          <t xml:space="preserve">ocr_extractor.py (PaddleOCR) + 이미지 크기 측정</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3427,19 +3435,19 @@
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-01</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -3449,24 +3457,24 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">레지스트리 등록</t>
+          <t xml:space="preserve">OcrExtractor, 이미지 크기</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">공유파일 — 즉시 푸시</t>
+          <t xml:space="preserve">배포 용량 확인용</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:19" ht="18" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.9</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 보안 강화 (UUID 파일 저장 + 경로 조작 방지)</t>
+          <t xml:space="preserve">2.1.8</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">extractor registry 등록 (dependencies.py)</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3474,9 +3482,9 @@
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46237</t>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -3486,7 +3494,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
@@ -3494,14 +3502,14 @@
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J40" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">extraction_service.py</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레지스트리 등록</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공유파일 — 즉시 푸시</t>
         </is>
       </c>
     </row>
@@ -3511,43 +3519,42 @@
           <t xml:space="preserve">2.1.9</t>
         </is>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 보안 강화 (UUID 저장 + 경로 조작 방지)</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="D41" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 보안 강화 (UUID 파일 저장 + 경로 조작 방지)</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-03</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">extraction_service.py</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
         </is>
@@ -3603,60 +3610,59 @@
     <row r="43" spans="1:19" ht="18" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.10</t>
-        </is>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDF 텍스트 + 이미지 OCR 통합 추출 (좌표 병합)</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
+          <t xml:space="preserve">2.1.11</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46236</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pdf_extractor.py · layout.py</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이미지 픽셀 → PDF 좌표 변환. ExtractMethod.HYBRID 산출</t>
+      <c r="J43" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_extractor.py</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동시 요청 시 OCR 엔진 충돌 방지</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:19" ht="18" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.11</t>
+          <t xml:space="preserve">2.1.12</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
+          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3666,12 +3672,12 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">46236</t>
-        </is>
-      </c>
-      <c r="G44" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46236</t>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -3684,74 +3690,73 @@
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ocr_extractor.py</t>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외 처리</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">동시 요청 시 OCR 엔진 충돌 방지</t>
+          <t xml:space="preserve">빈 결과 실패 처리, HWPX 내부 이미지 오류는 해당 이미지만 건너뜀</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:19" ht="18" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.11</t>
-        </is>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
+          <t xml:space="preserve">2.1.13</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS=45,000)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-02</t>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ocr_extractor.py</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동시 요청 시 엔진 충돌 방지</t>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">config.py, extractor</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-009 / 결정사항 12</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:19" ht="18" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.12</t>
+          <t xml:space="preserve">2.1.14</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
+          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -3781,40 +3786,39 @@
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">예외 처리</t>
+          <t xml:space="preserve">검증 로직, error_codes</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 결과 실패 처리, HWPX 내부 이미지 오류는 해당 이미지만 건너뜀</t>
+          <t xml:space="preserve">파일 크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:19" ht="18" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.12</t>
-        </is>
-      </c>
-      <c r="C47" s="5"/>
+          <t xml:space="preserve">2.1.15</t>
+        </is>
+      </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
+          <t xml:space="preserve">Tesseract 추출기 구현</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3829,87 +3833,86 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">예외 처리</t>
+          <t xml:space="preserve">tesseract_extractor.py</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">빈 결과 실패 처리. HWPX 내부 이미지 오류는 건너뜀</t>
+          <t xml:space="preserve">한국어·영어 학습 데이터. Dockerfile apt 패키지 추가</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:19" ht="18" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.13</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS=45,000)</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46237</t>
+          <t xml:space="preserve">2.1.16</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진 비교 API</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">config.py, extractor</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-009 / 결정사항 12</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocr_compare_router · service</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 1 근거 확보용</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:19" ht="18" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.13</t>
-        </is>
-      </c>
-      <c r="C49" s="5"/>
+          <t xml:space="preserve">2.1.17</t>
+        </is>
+      </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS)</t>
+          <t xml:space="preserve">EasyOCR 추출기 추가 및 비교 대상 확장</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3924,87 +3927,86 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">config.py · extractor</t>
+          <t xml:space="preserve">easyocr_extractor.py</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-010 · 결정사항 12</t>
+          <t xml:space="preserve">이미지 6종으로 확장. CPU 전용 torch 고정 (ISS-030)</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:19" ht="18" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.14</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
+          <t xml:space="preserve">2.1.18</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">텍스트 레이어 같은 줄 병합</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">최재정</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46237</t>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검증 로직, error_codes</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">파일 크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pdf_extractor.py</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-020. 줄 단위 요소화 후 병합</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:19" ht="18" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.14</t>
-        </is>
-      </c>
-      <c r="C51" s="5"/>
+          <t xml:space="preserve">2.1.19</t>
+        </is>
+      </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
+          <t xml:space="preserve">OCR 정확도 측정 방식 개선 (정답 데이터 기반)</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4019,25 +4021,24 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">검증 로직 · error_codes</t>
+          <t xml:space="preserve">ocr_ground_truth.py</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
+          <t xml:space="preserve">편집거리 기반. 결정사항 24</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:19" ht="18" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.15</t>
-        </is>
-      </c>
-      <c r="C52" s="5"/>
+          <t xml:space="preserve">2.1.20</t>
+        </is>
+      </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesseract 추출기 구현</t>
+          <t xml:space="preserve">OCR 비교 입력 형식 확장 (문서 → 이미지 변환)</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4047,12 +4048,12 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4067,40 +4068,39 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tesseract_extractor.py</t>
+          <t xml:space="preserve">ocr_compare_image_loader.py</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국어·영어 학습 데이터. Dockerfile apt 패키지 추가</t>
+          <t xml:space="preserve">결정사항 25</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:19" ht="18" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.16</t>
-        </is>
-      </c>
-      <c r="C53" s="5"/>
+          <t xml:space="preserve">2.1.21</t>
+        </is>
+      </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 엔진 비교 API</t>
+          <t xml:space="preserve">이미지 품질 분석 기반 전처리 동적 선택</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4115,40 +4115,39 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_compare_router · service</t>
+          <t xml:space="preserve">preprocessing.py · ocr_extractor.py</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 1 근거 확보용</t>
+          <t xml:space="preserve">품질 측정 후 필요한 단계만 적용. 처리 시간 3배 증가 (ISS-036)</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:19" ht="18" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.17</t>
-        </is>
-      </c>
-      <c r="C54" s="5"/>
+          <t xml:space="preserve">2.1.22</t>
+        </is>
+      </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EasyOCR 추출기 추가 및 비교 대상 확장</t>
+          <t xml:space="preserve">하이브리드 PDF 읽기 순서 처리</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4163,30 +4162,29 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">easyocr_extractor.py</t>
+          <t xml:space="preserve">reading_order.py</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지 6종으로 확장. CPU 전용 torch 고정 (ISS-030)</t>
+          <t xml:space="preserve">다단 문서 순서 복원. 표 영역 오인식 수정</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:19" ht="18" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.18</t>
-        </is>
-      </c>
-      <c r="C55" s="5"/>
+          <t xml:space="preserve">2.1.23</t>
+        </is>
+      </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">텍스트 레이어 같은 줄 병합</t>
+          <t xml:space="preserve">EasyOCR 메모리 격리 (별도 프로세스)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -4211,121 +4209,78 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pdf_extractor.py</t>
+          <t xml:space="preserve">easyocr_subprocess_extractor.py · workers/</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-020. 줄 단위 요소화 후 병합</t>
+          <t xml:space="preserve">ISS-035. 호출 종료 시 메모리 완전 회수</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:19" ht="18" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.1.19</t>
-        </is>
-      </c>
-      <c r="C56" s="5"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 정확도 측정 방식 개선 (정답 데이터 기반)</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ocr_ground_truth.py</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">편집거리 기반. 결정사항 24</t>
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:19" ht="18" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.20</t>
-        </is>
-      </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 비교 입력 형식 확장 (문서 → 이미지 변환)</t>
+          <t xml:space="preserve">2.2.1</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면 + 드래그앤드롭</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-01</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocr_compare_image_loader.py</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항 25</t>
+          <t xml:space="preserve">UploadPage</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:19" ht="18" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.21</t>
-        </is>
-      </c>
-      <c r="C58" s="5"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이미지 품질 분석 기반 전처리 동적 선택</t>
+          <t xml:space="preserve">2.2.2</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로딩 상태 UI (status 단계 표시)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -4335,12 +4290,12 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4350,30 +4305,29 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">preprocessing.py · ocr_extractor.py</t>
+          <t xml:space="preserve">Spinner/StatusBar</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">품질 측정 후 필요한 단계만 적용. 처리 시간 3배 증가 (ISS-036)</t>
+          <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:19" ht="18" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.22</t>
-        </is>
-      </c>
-      <c r="C59" s="5"/>
+          <t xml:space="preserve">2.2.3</t>
+        </is>
+      </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">하이브리드 PDF 읽기 순서 처리</t>
+          <t xml:space="preserve">원본 미리보기 + 추출 텍스트 비교 화면</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -4383,12 +4337,12 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4403,341 +4357,372 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reading_order.py</t>
+          <t xml:space="preserve">업로드 화면</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다단 문서 순서 복원. 표 영역 오인식 수정</t>
+          <t xml:space="preserve">본프로젝트 '영역별 수정' 기능의 읽기 전용 선행 구현</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:19" ht="18" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1.23</t>
-        </is>
-      </c>
-      <c r="C60" s="5"/>
+          <t xml:space="preserve">2.2.4</t>
+        </is>
+      </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EasyOCR 메모리 격리 (별도 프로세스)</t>
+          <t xml:space="preserve">업로드 화면 재구성 (드롭존 + 3단계 진행)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 화면</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목업 안3 반영. 공통 컴포넌트 재사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="18" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2.5</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 비교 화면</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">easyocr_subprocess_extractor.py · workers/</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-035. 호출 종료 시 메모리 완전 회수</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="18" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OcrComparePage</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/ocr-compare</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:19" ht="18" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2.1</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">업로드 화면 + 드래그앤드롭</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-01</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-02</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UploadPage</t>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI 분석 — 요약 / 카테고리  [B · 세현]</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:19" ht="18" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.2.2</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">로딩 상태 UI (status 단계 표시)</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-02</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-02</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spinner/StatusBar</t>
-        </is>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지시서 필수항목</t>
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:19" ht="18" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2.3</t>
-        </is>
-      </c>
-      <c r="C64" s="5"/>
+          <t xml:space="preserve">3.1.1</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">원본 미리보기 + 추출 텍스트 비교 화면</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
+          <t xml:space="preserve">prompts.py — 프롬프트 + PROMPT_VERSION</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 화면</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">본프로젝트 '영역별 수정' 기능의 읽기 전용 선행 구현</t>
+          <t xml:space="preserve">프롬프트 설계</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:19" ht="18" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2.4</t>
-        </is>
-      </c>
-      <c r="C65" s="5"/>
+          <t xml:space="preserve">3.1.2</t>
+        </is>
+      </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 화면 재구성 (드롭존 + 3단계 진행)</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
+          <t xml:space="preserve">summary_analyzer.py (async)</t>
+        </is>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46234</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">업로드 화면</t>
+          <t xml:space="preserve">SummaryAnalyzer</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">목업 안3 반영. 공통 컴포넌트 재사용</t>
+          <t xml:space="preserve">generate_with_meta 사용</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:19" ht="18" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2.5</t>
-        </is>
-      </c>
-      <c r="C66" s="5"/>
+          <t xml:space="preserve">3.1.3</t>
+        </is>
+      </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OCR 비교 화면</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
+          <t xml:space="preserve">category_analyzer.py (Literal로 값 고정)</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-01</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OcrComparePage</t>
+          <t xml:space="preserve">CategoryAnalyzer</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">/ocr-compare</t>
+          <t xml:space="preserve">값 고정 안 하면 C 필터 깨짐</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:19" ht="18" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI 분석 — 요약 / 카테고리  [B · 세현]</t>
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.4</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analysis_service.py + analysis_router.py (async)</t>
+        </is>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석 API</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">재분석 시 행 추가</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:19" ht="18" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백엔드</t>
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1.5</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">analyzer registry 등록 (dependencies.py)</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I68" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레지스트리 등록</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">공유파일 — 즉시 푸시</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:19" ht="18" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.1</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompts.py — 프롬프트 + PROMPT_VERSION</t>
+          <t xml:space="preserve">3.1.6</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
         </is>
       </c>
       <c r="E69" s="17" t="inlineStr">
@@ -4745,14 +4730,14 @@
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46234</t>
-        </is>
-      </c>
-      <c r="G69" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46234</t>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -4762,24 +4747,29 @@
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프롬프트 설계</t>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J69" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">openai_client.py</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JSON 모드 응답 강제 + 토큰·지연 계측 포함</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:19" ht="18" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.2</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">summary_analyzer.py (async)</t>
+          <t xml:space="preserve">3.1.7</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
         </is>
       </c>
       <c r="E70" s="17" t="inlineStr">
@@ -4787,14 +4777,14 @@
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46234</t>
-        </is>
-      </c>
-      <c r="G70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46234</t>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -4807,88 +4797,88 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SummaryAnalyzer</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">generate_with_meta 사용</t>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage.jsx</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A/B/C 파트 진입 구성</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:19" ht="18" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.3</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">category_analyzer.py (Literal로 값 고정)</t>
-        </is>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
+          <t xml:space="preserve">3.1.8</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토큰/지연/모델명 기록 검증</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I71" s="18" t="inlineStr">
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CategoryAnalyzer</t>
+          <t xml:space="preserve">analyses 컬럼 확인</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">값 고정 안 하면 C 필터 깨짐</t>
+          <t xml:space="preserve">분석 이력에 토큰·지연·모델명 기록 확인</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:19" ht="18" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.4</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">analysis_service.py + analysis_router.py (async)</t>
-        </is>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
+          <t xml:space="preserve">3.1.9</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OpenAI 실연동 전환 (계정 확보 후)</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4896,187 +4886,116 @@
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="I72" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 API</t>
+          <t xml:space="preserve">openai_client.py</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">재분석 시 행 추가</t>
+          <t xml:space="preserve">키 길이 164 / USE_FAKE_AI=False 확인 (ISS-031 해결 후)</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:19" ht="18" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.5</t>
+          <t xml:space="preserve">3.1.10</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyzer registry 등록 (dependencies.py)</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
+          <t xml:space="preserve">요약·분류 병렬 실행 최적화</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I73" s="18" t="inlineStr">
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">레지스트리 등록</t>
-        </is>
-      </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">공유파일 — 즉시 푸시</t>
+          <t xml:space="preserve">analysis_service.py</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-018. asyncio.gather 로 응답 시간 단축</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:19" ht="18" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1.6</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J74" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">openai_client.py</t>
-        </is>
-      </c>
-      <c r="K74" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구현 완료.</t>
-        </is>
-      </c>
+      <c r="A74" s="4"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="4"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
     </row>
     <row r="75" spans="1:19" ht="18" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1.7</t>
-        </is>
-      </c>
-      <c r="D75" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J75" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MainPage.jsx</t>
-        </is>
-      </c>
-      <c r="K75" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A/B/C 파트 진입 구성</t>
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.2</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:19" ht="18" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.8</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">토큰/지연/모델명 기록 검증</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
+          <t xml:space="preserve">3.2.1</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">분석 요청 / 진행 표시</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">박세현</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G76" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -5084,79 +5003,73 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyses 컬럼 확인</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">★ 본프로젝트 필수 데이터</t>
+          <t xml:space="preserve">analyze 연동</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:19" ht="18" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.8</t>
-        </is>
-      </c>
-      <c r="C77" s="5"/>
+          <t xml:space="preserve">3.2.2</t>
+        </is>
+      </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
+          <t xml:space="preserve">요약 / 카테고리 결과 컴포넌트</t>
+        </is>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">박세현</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46237</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">08-03</t>
         </is>
       </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
+      <c r="H77" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">openai_client.py</t>
+          <t xml:space="preserve">ResultView</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:19" ht="18" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1.9</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenAI 실연동 전환 (계정 확보 후)</t>
+          <t xml:space="preserve">3.2.3</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">최재정</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -5166,162 +5079,115 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MainPage.jsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조회 / 검색 / 출력  [C · 보현]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="18" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="18" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.1</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">document_service.py</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-02</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">openai_client.py</t>
-        </is>
-      </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그전까지 FakeClient</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="18" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1.9</t>
-        </is>
-      </c>
-      <c r="C79" s="5"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요약·분류 병렬 실행 최적화</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">최재정</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-03</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">analysis_service.py</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-018. asyncio.gather 로 응답 시간 단축</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="18" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1.10</t>
-        </is>
-      </c>
-      <c r="C80" s="5"/>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenAI 실연동 전환 (FAKE → 실제 호출)</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">.env · compose override</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-031 해결 후 전환. 요약·분류·근거 정상 생성 확인</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="18" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.2</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서비스</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:19" ht="18" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2.1</t>
+          <t xml:space="preserve">4.1.2</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">분석 요청 / 진행 표시</t>
-        </is>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46237</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46237</t>
+          <t xml:space="preserve">document_router.py — 목록/상세 (동기)</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-01</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -5329,36 +5195,41 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I82" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">analyze 연동</t>
+          <t xml:space="preserve">조회 API</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PageResponse 사용</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:19" ht="18" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2.2</t>
+          <t xml:space="preserve">4.1.3</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">요약 / 카테고리 결과 컴포넌트</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46237</t>
+          <t xml:space="preserve">검색 (q / document_type / category)</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -5366,37 +5237,41 @@
           <t xml:space="preserve">08-03</t>
         </is>
       </c>
-      <c r="H83" s="12" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I83" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ResultView</t>
+          <t xml:space="preserve">검색 API</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">파일명 + 본문 부분검색. 공백 정규화 포함 (ISS-034)</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:19" ht="18" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2.3</t>
-        </is>
-      </c>
-      <c r="C84" s="5"/>
+          <t xml:space="preserve">4.1.4</t>
+        </is>
+      </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
+          <t xml:space="preserve">다운로드 (.txt, 한글 파일명 대응)</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -5421,43 +5296,83 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MainPage.jsx</t>
+          <t xml:space="preserve">다운로드 API</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">filename*=UTF-8''. 줄바꿈 버그 ISS-016 수정</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:19" ht="18" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="B85" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">조회 / 검색 / 출력  [C · 보현]</t>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.1.5</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 (cascade + 업로드 파일 제거)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-03</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELETE API</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 18 변경으로 구현. cascade + 업로드 파일 제거</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:19" ht="18" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1</t>
+          <t xml:space="preserve">4.2</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">백엔드</t>
+          <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:19" ht="18" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1.1</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">document_service.py</t>
+          <t xml:space="preserve">4.2.1</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 화면</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -5487,19 +5402,24 @@
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">서비스</t>
+          <t xml:space="preserve">ListPage</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블 + 검색 + 페이징</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:19" ht="18" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1.2</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">document_router.py — 목록/상세 (동기)</t>
+          <t xml:space="preserve">4.2.2</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세 화면 (요약 + 카테고리)</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -5509,12 +5429,12 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -5529,24 +5449,24 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">조회 API</t>
+          <t xml:space="preserve">DetailPage</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PageResponse 사용</t>
+          <t xml:space="preserve">원문 접기·펼치기 + 분석 이력</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:19" ht="18" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1.3</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 (q / document_type / category)</t>
+          <t xml:space="preserve">4.2.3</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 UI + 다운로드 버튼</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -5576,24 +5496,19 @@
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">검색 API</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">파일명 + 본문 부분검색. 공백 정규화 포함 (ISS-034)</t>
+          <t xml:space="preserve">SearchBar</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:19" ht="18" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1.4</t>
+          <t xml:space="preserve">4.2.4</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">다운로드 (.txt, 한글 파일명 대응)</t>
+          <t xml:space="preserve">공통 컴포넌트 + 디자인 토큰</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -5623,39 +5538,39 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">다운로드 API</t>
+          <t xml:space="preserve">tokens.css · Badge · Spinner · ErrorBanner</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">filename*=UTF-8''. 줄바꿈 버그 ISS-016 수정</t>
+          <t xml:space="preserve">결정사항 15</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:19" ht="18" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1.5</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삭제 (cascade + 업로드 파일 제거)</t>
+          <t xml:space="preserve">4.2.5</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App.jsx 라우터 통합</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -5670,36 +5585,71 @@
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELETE API</t>
+          <t xml:space="preserve">App.jsx</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 18 변경으로 구현. cascade + 업로드 파일 제거</t>
+          <t xml:space="preserve">ISS-028. useState 토글 → react-router</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:19" ht="18" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2.6</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록에 업로드 진입점 추가</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최재정</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ListPage</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결정사항 19</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:19" ht="18" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.1</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 화면</t>
+          <t xml:space="preserve">4.2.7</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 + 상세 패널 (마스터-디테일)</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -5709,17 +5659,17 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-01</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -5734,19 +5684,19 @@
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">테이블 + 검색 + 페이징</t>
+          <t xml:space="preserve">결정사항 20. DocumentDetail 수정 없이 재사용</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:19" ht="18" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.2</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">상세 화면 (요약 + 카테고리)</t>
+          <t xml:space="preserve">4.2.8</t>
+        </is>
+      </c>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레이아웃 폭·여백 통일 및 헤더 정리</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -5756,12 +5706,12 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -5776,24 +5726,24 @@
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DetailPage</t>
+          <t xml:space="preserve">tokens.css · MainLayout</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">원문 접기·펼치기 + 분석 이력</t>
+          <t xml:space="preserve">컨테이너 1440px. --c-page-x 변수화</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:19" ht="18" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.3</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 UI + 다운로드 버튼</t>
+          <t xml:space="preserve">4.2.9</t>
+        </is>
+      </c>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홈 화면 기능 설명 영역 구성</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -5803,12 +5753,12 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -5823,35 +5773,39 @@
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SearchBar</t>
+          <t xml:space="preserve">MainPage</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능 확장 시 안내서 역할. 운영 메뉴얼과 문구 공유</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:19" ht="18" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.4</t>
-        </is>
-      </c>
-      <c r="C96" s="5"/>
+          <t xml:space="preserve">4.2.10</t>
+        </is>
+      </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통 컴포넌트 + 디자인 토큰</t>
+          <t xml:space="preserve">검색 공백 정규화</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -5866,40 +5820,39 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tokens.css · Badge · Spinner · ErrorBanner</t>
+          <t xml:space="preserve">document_repository.py</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 15</t>
+          <t xml:space="preserve">ISS-034. 중복 구현 통합 (결정사항 28)</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:19" ht="18" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.5</t>
-        </is>
-      </c>
-      <c r="C97" s="5"/>
+          <t xml:space="preserve">4.2.11</t>
+        </is>
+      </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">App.jsx 라우터 통합</t>
+          <t xml:space="preserve">삭제 화면 (확인 창 · 목록 갱신)</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5914,40 +5867,34 @@
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">App.jsx</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-028. useState 토글 → react-router</t>
+          <t xml:space="preserve">ListPage · DetailPage · DocumentDetail</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:19" ht="18" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.6</t>
-        </is>
-      </c>
-      <c r="C98" s="5"/>
+          <t xml:space="preserve">4.2.12</t>
+        </is>
+      </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">목록에 업로드 진입점 추가</t>
+          <t xml:space="preserve">UI/UX 전면 개선 및 공통 컴포넌트 리팩터링</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">최재정</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -5962,40 +5909,39 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ListPage</t>
+          <t xml:space="preserve">PageHeader · EmptyState · Icon · tokens.css</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 19</t>
+          <t xml:space="preserve">반응형 구조 정리. 삭제 기능은 새 디자인 시스템으로 이식</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:19" ht="18" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.7</t>
-        </is>
-      </c>
-      <c r="C99" s="5"/>
+          <t xml:space="preserve">4.2.13</t>
+        </is>
+      </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">목록 + 상세 패널 (마스터-디테일)</t>
+          <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -6010,136 +5956,63 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ListPage</t>
+          <t xml:space="preserve">NotFoundPage.jsx</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">결정사항 20. DocumentDetail 수정 없이 재사용</t>
+          <t xml:space="preserve">결정사항 27. 종전 빈 화면 개선</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:19" ht="18" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2.8</t>
-        </is>
-      </c>
-      <c r="C100" s="5"/>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">레이아웃 폭·여백 통일 및 헤더 정리</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tokens.css · MainLayout</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">컨테이너 1440px. --c-page-x 변수화</t>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 / 테스트 / 배포</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:19" ht="18" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2.9</t>
-        </is>
-      </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">홈 화면 기능 설명 영역 구성</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MainPage</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기능 확장 시 안내서 역할. 운영 메뉴얼과 문구 공유</t>
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:19" ht="18" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.10</t>
-        </is>
-      </c>
-      <c r="C102" s="5"/>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">검색 공백 정규화</t>
+          <t xml:space="preserve">5.1.1</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 마일스톤: E2E 전 구간 관통</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -6154,45 +6027,44 @@
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">document_repository.py</t>
+          <t xml:space="preserve">동작 확인</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISS-034. 중복 구현 통합 (결정사항 28)</t>
+          <t xml:space="preserve">08-03 관통 확인</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:19" ht="18" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.11</t>
-        </is>
-      </c>
-      <c r="C103" s="5"/>
-      <c r="D103" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삭제 화면 (확인 창 · 목록 갱신)</t>
+          <t xml:space="preserve">5.1.2</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API 계약 불일치 수정</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-02</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-03</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -6202,158 +6074,192 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ListPage · DetailPage · DocumentDetail</t>
+          <t xml:space="preserve">수정 이력</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-016 · ISS-017</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:19" ht="18" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2.12</t>
-        </is>
-      </c>
-      <c r="C104" s="5"/>
-      <c r="D104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI/UX 전면 개선 및 공통 컴포넌트 리팩터링</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PageHeader · EmptyState · Icon · tokens.css</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">반응형 구조 정리. 삭제 기능은 새 디자인 시스템으로 이식</t>
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:19" ht="18" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2.13</t>
-        </is>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">프론트엔드</t>
-        </is>
-      </c>
-      <c r="D105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
+          <t xml:space="preserve">5.2.1</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위 테스트 작성 / 실행</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박세현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">단위테스트결과서.xlsx</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66항목 전 항목 판정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" spans="1:19" ht="18" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2.2</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 테스트 시나리오 작성 / 실행</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80%</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합테스트시나리오.xlsx</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건은 08-06 오전</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="18" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2.3</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 / 이슈 리포트 정리</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-04</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">08-05</t>
         </is>
       </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NotFoundPage.jsx</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항 27. 종전 빈 화면 개선</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" spans="1:19" ht="18" customHeight="1">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통합 / 테스트 / 배포</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" spans="1:19" ht="18" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.1</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통합</t>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이슈리포트</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이슈관리 시트 46건 기록</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:19" ht="18" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1.1</t>
-        </is>
-      </c>
-      <c r="D108" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">★ 마일스톤: E2E 전 구간 관통</t>
+          <t xml:space="preserve">5.2.4</t>
+        </is>
+      </c>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">김보현</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -6363,135 +6269,135 @@
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">동작 확인</t>
+          <t xml:space="preserve">SQL 로그 · 개선 전후 수치</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03 관통 확인</t>
+          <t xml:space="preserve">결정사항 17. 본프로젝트 이관 검토</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:19" ht="18" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1.2</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">API 계약 불일치 수정</t>
+          <t xml:space="preserve">5.2.5</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">전원</t>
+          <t xml:space="preserve">박세현</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-02</t>
+          <t xml:space="preserve">08-04</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-03</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">60%</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비교 결과</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">confidence 기반 측정 완료. 정답 데이터 기반 측정 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" spans="1:19" ht="18" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2.6</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">100%</t>
         </is>
       </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">수정 이력</t>
-        </is>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-016 · ISS-017</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" spans="1:19" ht="18" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">csv · xlsx</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISS-037. UTF-8 통일 · 이슈 단일 표 재번호 (결정사항 29)</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:19" ht="18" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2.1</t>
-        </is>
-      </c>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단위 테스트 작성 / 실행</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">단위테스트결과서.xlsx</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66항목 전 항목 판정 완료</t>
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">배포</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:19" ht="18" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2.2</t>
+          <t xml:space="preserve">5.3.1</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">통합 테스트 시나리오 작성 / 실행</t>
+          <t xml:space="preserve">프론트엔드 컨테이너 검증</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -6506,39 +6412,34 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">80%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">통합테스트시나리오.xlsx</t>
-        </is>
-      </c>
-      <c r="K112" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건은 08-06 오전</t>
+          <t xml:space="preserve">frontend Dockerfile</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:19" ht="18" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2.3</t>
+          <t xml:space="preserve">5.3.2</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 / 이슈 리포트 정리</t>
+          <t xml:space="preserve">docker compose 전체 3컨테이너 기동 검증</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -6548,7 +6449,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-05</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -6558,39 +6459,34 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100%</t>
+          <t xml:space="preserve">0%</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이슈리포트</t>
+          <t xml:space="preserve">배포 확인</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">이슈관리 시트 46건 기록</t>
+          <t xml:space="preserve">PaddleOCR 포함 이미지</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:19" ht="18" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2.4</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
-        </is>
-      </c>
-      <c r="D114" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
+          <t xml:space="preserve">5.3.3</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영 메뉴얼 / 배포 문서</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -6600,160 +6496,115 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영 메뉴얼</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지시서 필수항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" spans="1:19" ht="18" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산출물 / 발표 준비</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="18" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문서 산출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="18" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1.1</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">프로젝트 완료 보고서</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">김보현</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">08-06</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">0%</t>
         </is>
       </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SQL 로그 · 개선 전후 수치</t>
-        </is>
-      </c>
-      <c r="K114" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항 17. 본프로젝트 이관 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" spans="1:19" ht="18" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2.5</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
-        </is>
-      </c>
-      <c r="D115" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="I115" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60%</t>
-        </is>
-      </c>
-      <c r="J115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비교 결과</t>
-        </is>
-      </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">confidence 기반 측정 완료. 정답 데이터 기반 측정 남음</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" spans="1:19" ht="18" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2.6</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">테스트</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I116" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J116" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">csv · xlsx</t>
-        </is>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-037. UTF-8 통일 · 이슈 단일 표 재번호 (결정사항 29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" spans="1:19" ht="18" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.3</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">배포</t>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료 보고서</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:19" ht="18" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3.1</t>
+          <t xml:space="preserve">6.1.2</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">프론트엔드 컨테이너 검증</t>
+          <t xml:space="preserve">산출물 11종 최종 점검</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -6763,17 +6614,17 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-04</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -6783,71 +6634,36 @@
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">frontend Dockerfile</t>
+          <t xml:space="preserve">제출 목록</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:19" ht="18" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.3.2</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">docker compose 전체 3컨테이너 기동 검증</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">배포 확인</t>
-        </is>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PaddleOCR 포함 이미지</t>
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:19" ht="18" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3.3</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">운영 메뉴얼 / 배포 문서</t>
+          <t xml:space="preserve">6.2.1</t>
+        </is>
+      </c>
+      <c r="D120" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 코드 프리즈</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -6867,63 +6683,133 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">100%</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05 코드 프리즈. 이후 산출물 작업만 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="18" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2.2</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표자료(PPT) 작성 — 목차 5장</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-06</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">0%</t>
         </is>
       </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">운영 메뉴얼</t>
-        </is>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지시서 필수항목</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="18" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물 / 발표 준비</t>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표자료.pptx</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원 분담</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:19" ht="18" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.1</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">문서 산출물</t>
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.2.3</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표영상 녹화 / 편집</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전원</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-05</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08-06</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0%</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발표영상.zip</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시나리오 사전 작성</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:19" ht="18" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1.1</t>
+          <t xml:space="preserve">6.2.4</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">프로젝트 완료 보고서</t>
+          <t xml:space="preserve">발표 리허설 2회 (시간 측정)</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-05</t>
+          <t xml:space="preserve">08-06</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -6933,7 +6819,7 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
@@ -6943,39 +6829,39 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">완료 보고서</t>
+          <t xml:space="preserve">리허설 기록</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">지시서 필수항목</t>
+          <t xml:space="preserve">전원 발표 필수</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:19" ht="18" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1.2</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물 11종 최종 점검</t>
+          <t xml:space="preserve">6.2.5</t>
+        </is>
+      </c>
+      <c r="D124" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">★ 최종 발표</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">김보현</t>
+          <t xml:space="preserve">전원</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-06</t>
+          <t xml:space="preserve">08-07</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">08-06</t>
+          <t xml:space="preserve">08-07</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -6990,559 +6876,31 @@
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">제출 목록</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" spans="1:19" ht="18" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2</t>
-        </is>
-      </c>
-      <c r="C125" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발표</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" spans="1:19" ht="18" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2.1</t>
-        </is>
-      </c>
-      <c r="D126" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">★ 코드 프리즈</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J126" s="5" t="inlineStr">
-        <is>
           <t xml:space="preserve">-</t>
         </is>
       </c>
-      <c r="K126" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05 코드 프리즈. 이후 산출물 작업만 진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" spans="1:19" ht="18" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2.2</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발표자료(PPT) 작성 — 목차 5장</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발표자료.pptx</t>
-        </is>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원 분담</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" spans="1:19" ht="18" customHeight="1">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2.3</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발표영상 녹화 / 편집</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I128" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발표영상.zip</t>
-        </is>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시나리오 사전 작성</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" spans="1:19" ht="18" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2.4</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">발표 리허설 2회 (시간 측정)</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J129" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리허설 기록</t>
-        </is>
-      </c>
-      <c r="K129" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원 발표 필수</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" spans="1:19" ht="18" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.2.5</t>
-        </is>
-      </c>
-      <c r="D130" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">★ 최종 발표</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전원</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-07</t>
-        </is>
-      </c>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-07</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J130" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="K130" s="5" t="inlineStr">
+      <c r="K124" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">팀원 전원 참여</t>
         </is>
       </c>
     </row>
-    <row r="131" spans="1:19" ht="18" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WBS ID</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대분류</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">중분류</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작업명</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">담당</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시작일</t>
-        </is>
-      </c>
-      <c r="G131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종료일</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일수</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">진행률</t>
-        </is>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7/31
-(금)</t>
-        </is>
-      </c>
-      <c r="M131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1
-(토)</t>
-        </is>
-      </c>
-      <c r="N131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/2
-(일)</t>
-        </is>
-      </c>
-      <c r="O131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/3
-(월)</t>
-        </is>
-      </c>
-      <c r="P131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/4
-(화)</t>
-        </is>
-      </c>
-      <c r="Q131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/5
-(수)</t>
-        </is>
-      </c>
-      <c r="R131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/6
-(목)</t>
-        </is>
-      </c>
-      <c r="S131" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/7
-(금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" spans="1:19" ht="18" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2.13</t>
-        </is>
-      </c>
-      <c r="C132" s="5"/>
-      <c r="D132" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J132" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NotFoundPage.jsx</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항 27. 종전 빈 화면 개선</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" spans="1:19" ht="18" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2.4</t>
-        </is>
-      </c>
-      <c r="C133" s="5"/>
-      <c r="D133" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0%</t>
-        </is>
-      </c>
-      <c r="J133" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SQL 로그 · 개선 전후 수치</t>
-        </is>
-      </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">결정사항 17. 본프로젝트 이관 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" spans="1:19" ht="18" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2.5</t>
-        </is>
-      </c>
-      <c r="C134" s="5"/>
-      <c r="D134" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">박세현</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-04</t>
-        </is>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-06</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60%</t>
-        </is>
-      </c>
-      <c r="J134" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비교 결과</t>
-        </is>
-      </c>
-      <c r="K134" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">confidence 기반 측정 완료. 정답 데이터 기반 측정 남음</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" spans="1:19" ht="18" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2.6</t>
-        </is>
-      </c>
-      <c r="C135" s="5"/>
-      <c r="D135" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">김보현</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08-05</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100%</t>
-        </is>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">csv · xlsx</t>
-        </is>
-      </c>
-      <c r="K135" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISS-037. UTF-8 통일 · 이슈 단일 표 재번호 (결정사항 29)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="16.5" customHeight="1"/>
-    <row r="137" ht="16.5" customHeight="1"/>
-    <row r="138" ht="16.5" customHeight="1"/>
-    <row r="139" ht="16.5" customHeight="1"/>
-    <row r="140" ht="16.5" customHeight="1"/>
+    <row r="125" spans="1:19" ht="18" customHeight="1"/>
+    <row r="126" spans="1:19" ht="18" customHeight="1"/>
+    <row r="127" spans="1:19" ht="18" customHeight="1"/>
+    <row r="128" spans="1:19" ht="18" customHeight="1"/>
+    <row r="129" spans="1:19" ht="18" customHeight="1"/>
+    <row r="130" spans="1:19" ht="18" customHeight="1"/>
+    <row r="131" spans="1:19" ht="18" customHeight="1"/>
+    <row r="132" spans="1:19" ht="18" customHeight="1"/>
+    <row r="133" spans="1:19" ht="18" customHeight="1"/>
+    <row r="134" spans="1:19" ht="18" customHeight="1"/>
+    <row r="135" spans="1:19" ht="18" customHeight="1"/>
+    <row r="136" spans="1:19" ht="18" customHeight="1"/>
+    <row r="137" spans="1:19" ht="18" customHeight="1"/>
+    <row r="138" spans="1:19" ht="18" customHeight="1"/>
+    <row r="139" spans="1:19" ht="18" customHeight="1"/>
+    <row r="140" spans="1:19" ht="18" customHeight="1"/>
     <row r="141" ht="16.5" customHeight="1"/>
     <row r="142" ht="16.5" customHeight="1"/>
     <row r="143" ht="16.5" customHeight="1"/>

--- a/관리/WBS(작업분할구조도)_v1.xlsx
+++ b/관리/WBS(작업분할구조도)_v1.xlsx
@@ -2159,6 +2159,23 @@
           <t xml:space="preserve">프로젝트 기획 및 개발환경 구축</t>
         </is>
       </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
     </row>
     <row r="7" spans="1:19" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -2166,11 +2183,28 @@
           <t xml:space="preserve">1.1</t>
         </is>
       </c>
+      <c r="B7" s="7"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">요구사항 분석 / 기술 결정</t>
         </is>
       </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -2178,6 +2212,8 @@
           <t xml:space="preserve">1.1.1</t>
         </is>
       </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">과제 지시서 분석 및 요구사항 도출</t>
@@ -2213,6 +2249,15 @@
           <t xml:space="preserve">요구사항 체크리스트</t>
         </is>
       </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
     </row>
     <row r="9" spans="1:19" ht="18" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -2220,6 +2265,8 @@
           <t xml:space="preserve">1.1.2</t>
         </is>
       </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">문서 도메인 / 카테고리 값 정의</t>
@@ -2260,6 +2307,14 @@
           <t xml:space="preserve">카테고리 6종 확정 (계약·약관 명칭 변경은 미결정)</t>
         </is>
       </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2267,6 +2322,8 @@
           <t xml:space="preserve">1.1.3</t>
         </is>
       </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">텍스트 추출 전략 수립 (레이어 우선 + OCR)</t>
@@ -2302,6 +2359,15 @@
           <t xml:space="preserve">기술 검토서</t>
         </is>
       </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
     </row>
     <row r="11" spans="1:19" ht="18" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -2309,6 +2375,8 @@
           <t xml:space="preserve">1.1.4</t>
         </is>
       </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 엔진 선정 — PaddleOCR v5 확정</t>
@@ -2349,6 +2417,14 @@
           <t xml:space="preserve">컨테이너 실행 테스트 완료</t>
         </is>
       </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
     </row>
     <row r="12" spans="1:19" ht="18" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2356,6 +2432,8 @@
           <t xml:space="preserve">1.1.5</t>
         </is>
       </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DB 선정 — PostgreSQL (본프로젝트까지 단일 사용)</t>
@@ -2396,6 +2474,14 @@
           <t xml:space="preserve">DB 교체 없이 연속 사용</t>
         </is>
       </c>
+      <c r="L12" s="10"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
     </row>
     <row r="13" spans="1:19" ht="18" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -2403,6 +2489,7 @@
           <t xml:space="preserve">1.1.6</t>
         </is>
       </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">샘플 문서 수집 (카테고리별)</t>
@@ -2450,11 +2537,28 @@
           <t xml:space="preserve">1.2</t>
         </is>
       </c>
+      <c r="B14" s="7"/>
       <c r="C14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">프로젝트 계획</t>
         </is>
       </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
     </row>
     <row r="15" spans="1:19" ht="18" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2462,6 +2566,8 @@
           <t xml:space="preserve">1.2.1</t>
         </is>
       </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">역할 분담 확정 (A 최재정 / B 박세현 / C 김보현)</t>
@@ -2497,6 +2603,15 @@
           <t xml:space="preserve">역할표</t>
         </is>
       </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
     </row>
     <row r="16" spans="1:19" ht="18" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2504,6 +2619,8 @@
           <t xml:space="preserve">1.2.2</t>
         </is>
       </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">WBS 작성 / 갱신</t>
@@ -2544,6 +2661,14 @@
           <t xml:space="preserve">이슈 37건 · 결정사항 29건 반영. 최종 정리 남음</t>
         </is>
       </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="4"/>
     </row>
     <row r="17" spans="1:19" ht="18" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2551,6 +2676,8 @@
           <t xml:space="preserve">1.2.3</t>
         </is>
       </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Git 브랜치 전략 / 공유파일 규칙 합의</t>
@@ -2591,6 +2718,14 @@
           <t xml:space="preserve">feature/기능명 (기능 단위)</t>
         </is>
       </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
     </row>
     <row r="18" spans="1:19" ht="18" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2598,6 +2733,8 @@
           <t xml:space="preserve">1.2.4</t>
         </is>
       </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">주말 작업 가능 여부 확인 — 가능 확정</t>
@@ -2638,6 +2775,14 @@
           <t xml:space="preserve">시나리오 A 적용</t>
         </is>
       </c>
+      <c r="L18" s="10"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
     </row>
     <row r="19" spans="1:19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -2645,11 +2790,28 @@
           <t xml:space="preserve">1.3</t>
         </is>
       </c>
+      <c r="B19" s="7"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">설계</t>
         </is>
       </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
     </row>
     <row r="20" spans="1:19" ht="18" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -2657,6 +2819,8 @@
           <t xml:space="preserve">1.3.1</t>
         </is>
       </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">API 엔드포인트 6종 합의 완료</t>
@@ -2697,6 +2861,14 @@
           <t xml:space="preserve">경로/필드명(snake_case)/status 확정</t>
         </is>
       </c>
+      <c r="L20" s="10"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
     </row>
     <row r="21" spans="1:19" ht="18" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -2704,6 +2876,8 @@
           <t xml:space="preserve">1.3.2</t>
         </is>
       </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
       <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DB 모델 설계 및 ERD 작성</t>
@@ -2744,6 +2918,14 @@
           <t xml:space="preserve">ERD.png 업로드 완료</t>
         </is>
       </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
     </row>
     <row r="22" spans="1:19" ht="18" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2751,6 +2933,8 @@
           <t xml:space="preserve">1.3.3</t>
         </is>
       </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">화면 정의서 작성</t>
@@ -2791,6 +2975,14 @@
           <t xml:space="preserve">5화면 · 캡처 7장 · 흐름도 완료. PDF 저장 남음</t>
         </is>
       </c>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
     </row>
     <row r="23" spans="1:19" ht="18" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -2798,11 +2990,28 @@
           <t xml:space="preserve">1.4</t>
         </is>
       </c>
+      <c r="B23" s="7"/>
       <c r="C23" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">개발환경 구축</t>
         </is>
       </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
     </row>
     <row r="24" spans="1:19" ht="18" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -2810,6 +3019,8 @@
           <t xml:space="preserve">1.4.1</t>
         </is>
       </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Git / Docker 설치 (전원)</t>
@@ -2845,6 +3056,15 @@
           <t xml:space="preserve">설치 확인</t>
         </is>
       </c>
+      <c r="K24" s="5"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
     </row>
     <row r="25" spans="1:19" ht="18" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -2852,6 +3072,8 @@
           <t xml:space="preserve">1.4.2</t>
         </is>
       </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">docker-compose 구성 (db + api + frontend)</t>
@@ -2892,6 +3114,14 @@
           <t xml:space="preserve">healthcheck, env_file 포함</t>
         </is>
       </c>
+      <c r="L25" s="10"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
     </row>
     <row r="26" spans="1:19" ht="18" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -2899,6 +3129,8 @@
           <t xml:space="preserve">1.4.3</t>
         </is>
       </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">공통 인프라 core/ 구현</t>
@@ -2934,6 +3166,15 @@
           <t xml:space="preserve">config/예외/로깅/미들웨어/트랜잭션</t>
         </is>
       </c>
+      <c r="K26" s="5"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
     </row>
     <row r="27" spans="1:19" ht="18" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -2941,6 +3182,8 @@
           <t xml:space="preserve">1.4.9</t>
         </is>
       </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">★ 마일스톤: 전원 compose up + /health 200</t>
@@ -2966,6 +3209,7 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
+      <c r="I27" s="4"/>
       <c r="J27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">동작 확인</t>
@@ -2976,6 +3220,14 @@
           <t xml:space="preserve">미달 시 D2 블로킹</t>
         </is>
       </c>
+      <c r="L27" s="20"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
     </row>
     <row r="28" spans="1:19" ht="18" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -2983,6 +3235,7 @@
           <t xml:space="preserve">1.4.10</t>
         </is>
       </c>
+      <c r="C28" s="5"/>
       <c r="D28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">프론트엔드 프로젝트 초기 구성 (Vite + React)</t>
@@ -3025,6 +3278,7 @@
           <t xml:space="preserve">1.4.11</t>
         </is>
       </c>
+      <c r="C29" s="5"/>
       <c r="D29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">requirements.txt 의존성 정리 및 중복 제거</t>
@@ -3072,6 +3326,7 @@
           <t xml:space="preserve">1.4.12</t>
         </is>
       </c>
+      <c r="C30" s="5"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">개인 실행 환경 분리 (compose override)</t>
@@ -3124,6 +3379,23 @@
           <t xml:space="preserve">업로드 / 텍스트 추출  [A · 재정]</t>
         </is>
       </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
@@ -3131,11 +3403,28 @@
           <t xml:space="preserve">2.1</t>
         </is>
       </c>
+      <c r="B32" s="7"/>
       <c r="C32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">백엔드</t>
         </is>
       </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
     </row>
     <row r="33" spans="1:19" ht="18" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -3143,6 +3432,8 @@
           <t xml:space="preserve">2.1.1</t>
         </is>
       </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">upload_router.py — POST /api/documents</t>
@@ -3183,6 +3474,14 @@
           <t xml:space="preserve">동기 라우터</t>
         </is>
       </c>
+      <c r="L33" s="4"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
     </row>
     <row r="34" spans="1:19" ht="18" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -3190,6 +3489,8 @@
           <t xml:space="preserve">2.1.2</t>
         </is>
       </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">extraction_service.py — 업로드/추출 로직</t>
@@ -3230,6 +3531,14 @@
           <t xml:space="preserve">Repository 경유</t>
         </is>
       </c>
+      <c r="L34" s="4"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
     </row>
     <row r="35" spans="1:19" ht="18" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -3237,6 +3546,8 @@
           <t xml:space="preserve">2.1.3</t>
         </is>
       </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">pdf_extractor.py (PyMuPDF)</t>
@@ -3277,6 +3588,14 @@
           <t xml:space="preserve">주 경로</t>
         </is>
       </c>
+      <c r="L35" s="4"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
     </row>
     <row r="36" spans="1:19" ht="18" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -3284,6 +3603,8 @@
           <t xml:space="preserve">2.1.4</t>
         </is>
       </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">파일 검증 (10MB / 30p / 확장자)</t>
@@ -3324,6 +3645,14 @@
           <t xml:space="preserve">registry.get()이 확장자 검증</t>
         </is>
       </c>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
     </row>
     <row r="37" spans="1:19" ht="18" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -3331,6 +3660,8 @@
           <t xml:space="preserve">2.1.5</t>
         </is>
       </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">docx / hwpx extractor</t>
@@ -3371,6 +3702,14 @@
           <t xml:space="preserve">구형 HWP 제외</t>
         </is>
       </c>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
     </row>
     <row r="38" spans="1:19" ht="18" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -3378,6 +3717,8 @@
           <t xml:space="preserve">2.1.6</t>
         </is>
       </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">requirements OCR 주석 해제 + 전원 재빌드 공지</t>
@@ -3418,6 +3759,14 @@
           <t xml:space="preserve">★ 사전 공지 필수</t>
         </is>
       </c>
+      <c r="L38" s="10"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
     </row>
     <row r="39" spans="1:19" ht="18" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -3425,6 +3774,8 @@
           <t xml:space="preserve">2.1.7</t>
         </is>
       </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
       <c r="D39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ocr_extractor.py (PaddleOCR) + 이미지 크기 측정</t>
@@ -3465,6 +3816,14 @@
           <t xml:space="preserve">배포 용량 확인용</t>
         </is>
       </c>
+      <c r="L39" s="10"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
     </row>
     <row r="40" spans="1:19" ht="18" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -3472,6 +3831,8 @@
           <t xml:space="preserve">2.1.8</t>
         </is>
       </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">extractor registry 등록 (dependencies.py)</t>
@@ -3512,6 +3873,14 @@
           <t xml:space="preserve">공유파일 — 즉시 푸시</t>
         </is>
       </c>
+      <c r="L40" s="4"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
     </row>
     <row r="41" spans="1:19" ht="18" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -3519,6 +3888,8 @@
           <t xml:space="preserve">2.1.9</t>
         </is>
       </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">업로드 보안 강화 (UUID 파일 저장 + 경로 조작 방지)</t>
@@ -3559,6 +3930,14 @@
           <t xml:space="preserve">원본 파일명 그대로 저장 시 경로 조작 위험 제거</t>
         </is>
       </c>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -3566,6 +3945,8 @@
           <t xml:space="preserve">2.1.10</t>
         </is>
       </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
       <c r="D42" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">PDF 텍스트 + 이미지 OCR 통합 추출 (좌표 기반 병합)</t>
@@ -3606,6 +3987,14 @@
           <t xml:space="preserve">이미지 픽셀→PDF 좌표 변환. ExtractMethod.HYBRID</t>
         </is>
       </c>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
     </row>
     <row r="43" spans="1:19" ht="18" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -3613,6 +4002,8 @@
           <t xml:space="preserve">2.1.11</t>
         </is>
       </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
       <c r="D43" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 인스턴스 공유 및 동시 실행 제어 (Lock)</t>
@@ -3653,6 +4044,14 @@
           <t xml:space="preserve">동시 요청 시 OCR 엔진 충돌 방지</t>
         </is>
       </c>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
     </row>
     <row r="44" spans="1:19" ht="18" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -3660,6 +4059,8 @@
           <t xml:space="preserve">2.1.12</t>
         </is>
       </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
       <c r="D44" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">추출 실패 / 부분 실패 처리</t>
@@ -3700,6 +4101,14 @@
           <t xml:space="preserve">빈 결과 실패 처리, HWPX 내부 이미지 오류는 해당 이미지만 건너뜀</t>
         </is>
       </c>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
     </row>
     <row r="45" spans="1:19" ht="18" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -3707,6 +4116,8 @@
           <t xml:space="preserve">2.1.13</t>
         </is>
       </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
       <c r="D45" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">글자 수 상한 적용 (MAX_EXTRACTED_CHARS=45,000)</t>
@@ -3747,6 +4158,14 @@
           <t xml:space="preserve">ISS-009 / 결정사항 12</t>
         </is>
       </c>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
     </row>
     <row r="46" spans="1:19" ht="18" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
@@ -3754,6 +4173,8 @@
           <t xml:space="preserve">2.1.14</t>
         </is>
       </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
       <c r="D46" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">업로드 검증 조기화 및 에러 메시지 통일</t>
@@ -3794,6 +4215,14 @@
           <t xml:space="preserve">파일 크기·페이지 수를 추출 전에 검사해 불필요한 처리 제거</t>
         </is>
       </c>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
     </row>
     <row r="47" spans="1:19" ht="18" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -3801,6 +4230,7 @@
           <t xml:space="preserve">2.1.15</t>
         </is>
       </c>
+      <c r="C47" s="5"/>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">Tesseract 추출기 구현</t>
@@ -3848,6 +4278,7 @@
           <t xml:space="preserve">2.1.16</t>
         </is>
       </c>
+      <c r="C48" s="5"/>
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 엔진 비교 API</t>
@@ -3895,6 +4326,7 @@
           <t xml:space="preserve">2.1.17</t>
         </is>
       </c>
+      <c r="C49" s="5"/>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">EasyOCR 추출기 추가 및 비교 대상 확장</t>
@@ -3942,6 +4374,7 @@
           <t xml:space="preserve">2.1.18</t>
         </is>
       </c>
+      <c r="C50" s="5"/>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">텍스트 레이어 같은 줄 병합</t>
@@ -3989,6 +4422,7 @@
           <t xml:space="preserve">2.1.19</t>
         </is>
       </c>
+      <c r="C51" s="5"/>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 정확도 측정 방식 개선 (정답 데이터 기반)</t>
@@ -4036,6 +4470,7 @@
           <t xml:space="preserve">2.1.20</t>
         </is>
       </c>
+      <c r="C52" s="5"/>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 비교 입력 형식 확장 (문서 → 이미지 변환)</t>
@@ -4083,6 +4518,7 @@
           <t xml:space="preserve">2.1.21</t>
         </is>
       </c>
+      <c r="C53" s="5"/>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">이미지 품질 분석 기반 전처리 동적 선택</t>
@@ -4130,6 +4566,7 @@
           <t xml:space="preserve">2.1.22</t>
         </is>
       </c>
+      <c r="C54" s="5"/>
       <c r="D54" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">하이브리드 PDF 읽기 순서 처리</t>
@@ -4177,6 +4614,7 @@
           <t xml:space="preserve">2.1.23</t>
         </is>
       </c>
+      <c r="C55" s="5"/>
       <c r="D55" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">EasyOCR 메모리 격리 (별도 프로세스)</t>
@@ -4224,11 +4662,28 @@
           <t xml:space="preserve">2.2</t>
         </is>
       </c>
+      <c r="B56" s="7"/>
       <c r="C56" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="7"/>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+      <c r="M56" s="7"/>
+      <c r="N56" s="7"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
     </row>
     <row r="57" spans="1:19" ht="18" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -4236,6 +4691,8 @@
           <t xml:space="preserve">2.2.1</t>
         </is>
       </c>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
       <c r="D57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">업로드 화면 + 드래그앤드롭</t>
@@ -4271,6 +4728,15 @@
           <t xml:space="preserve">UploadPage</t>
         </is>
       </c>
+      <c r="K57" s="5"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
     </row>
     <row r="58" spans="1:19" ht="18" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -4278,6 +4744,8 @@
           <t xml:space="preserve">2.2.2</t>
         </is>
       </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">로딩 상태 UI (status 단계 표시)</t>
@@ -4318,6 +4786,14 @@
           <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
     </row>
     <row r="59" spans="1:19" ht="18" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -4325,6 +4801,7 @@
           <t xml:space="preserve">2.2.3</t>
         </is>
       </c>
+      <c r="C59" s="5"/>
       <c r="D59" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">원본 미리보기 + 추출 텍스트 비교 화면</t>
@@ -4372,6 +4849,7 @@
           <t xml:space="preserve">2.2.4</t>
         </is>
       </c>
+      <c r="C60" s="5"/>
       <c r="D60" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">업로드 화면 재구성 (드롭존 + 3단계 진행)</t>
@@ -4419,6 +4897,7 @@
           <t xml:space="preserve">2.2.5</t>
         </is>
       </c>
+      <c r="C61" s="5"/>
       <c r="D61" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 비교 화면</t>
@@ -4471,6 +4950,23 @@
           <t xml:space="preserve">AI 분석 — 요약 / 카테고리  [B · 세현]</t>
         </is>
       </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
     </row>
     <row r="63" spans="1:19" ht="18" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -4478,11 +4974,28 @@
           <t xml:space="preserve">3.1</t>
         </is>
       </c>
+      <c r="B63" s="7"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">백엔드</t>
         </is>
       </c>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="7"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="7"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="7"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7"/>
+      <c r="S63" s="7"/>
     </row>
     <row r="64" spans="1:19" ht="18" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -4490,6 +5003,8 @@
           <t xml:space="preserve">3.1.1</t>
         </is>
       </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
       <c r="D64" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">prompts.py — 프롬프트 + PROMPT_VERSION</t>
@@ -4525,6 +5040,15 @@
           <t xml:space="preserve">프롬프트 설계</t>
         </is>
       </c>
+      <c r="K64" s="5"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
     </row>
     <row r="65" spans="1:19" ht="18" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -4532,6 +5056,8 @@
           <t xml:space="preserve">3.1.2</t>
         </is>
       </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
       <c r="D65" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">summary_analyzer.py (async)</t>
@@ -4572,6 +5098,14 @@
           <t xml:space="preserve">generate_with_meta 사용</t>
         </is>
       </c>
+      <c r="L65" s="4"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
     </row>
     <row r="66" spans="1:19" ht="18" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
@@ -4579,6 +5113,8 @@
           <t xml:space="preserve">3.1.3</t>
         </is>
       </c>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
       <c r="D66" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">category_analyzer.py (Literal로 값 고정)</t>
@@ -4619,6 +5155,14 @@
           <t xml:space="preserve">값 고정 안 하면 C 필터 깨짐</t>
         </is>
       </c>
+      <c r="L66" s="4"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
     </row>
     <row r="67" spans="1:19" ht="18" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
@@ -4626,6 +5170,8 @@
           <t xml:space="preserve">3.1.4</t>
         </is>
       </c>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">analysis_service.py + analysis_router.py (async)</t>
@@ -4666,6 +5212,14 @@
           <t xml:space="preserve">재분석 시 행 추가</t>
         </is>
       </c>
+      <c r="L67" s="4"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="23"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
     </row>
     <row r="68" spans="1:19" ht="18" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
@@ -4673,6 +5227,8 @@
           <t xml:space="preserve">3.1.5</t>
         </is>
       </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
       <c r="D68" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">analyzer registry 등록 (dependencies.py)</t>
@@ -4713,6 +5269,14 @@
           <t xml:space="preserve">공유파일 — 즉시 푸시</t>
         </is>
       </c>
+      <c r="L68" s="4"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
     </row>
     <row r="69" spans="1:19" ht="18" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
@@ -4720,6 +5284,8 @@
           <t xml:space="preserve">3.1.6</t>
         </is>
       </c>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
       <c r="D69" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenAI 클라이언트 구현 (JSON 모드 + 토큰·지연 기록)</t>
@@ -4760,6 +5326,14 @@
           <t xml:space="preserve">JSON 모드 응답 강제 + 토큰·지연 계측 포함</t>
         </is>
       </c>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
     </row>
     <row r="70" spans="1:19" ht="18" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
@@ -4767,6 +5341,8 @@
           <t xml:space="preserve">3.1.7</t>
         </is>
       </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
       <c r="D70" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
@@ -4807,6 +5383,14 @@
           <t xml:space="preserve">A/B/C 파트 진입 구성</t>
         </is>
       </c>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="10"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
     </row>
     <row r="71" spans="1:19" ht="18" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
@@ -4814,6 +5398,8 @@
           <t xml:space="preserve">3.1.8</t>
         </is>
       </c>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
       <c r="D71" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">토큰/지연/모델명 기록 검증</t>
@@ -4854,6 +5440,14 @@
           <t xml:space="preserve">분석 이력에 토큰·지연·모델명 기록 확인</t>
         </is>
       </c>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="10"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
     </row>
     <row r="72" spans="1:19" ht="18" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
@@ -4861,6 +5455,8 @@
           <t xml:space="preserve">3.1.9</t>
         </is>
       </c>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">OpenAI 실연동 전환 (계정 확보 후)</t>
@@ -4901,6 +5497,14 @@
           <t xml:space="preserve">키 길이 164 / USE_FAKE_AI=False 확인 (ISS-031 해결 후)</t>
         </is>
       </c>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="10"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
     </row>
     <row r="73" spans="1:19" ht="18" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
@@ -4908,6 +5512,7 @@
           <t xml:space="preserve">3.1.10</t>
         </is>
       </c>
+      <c r="C73" s="5"/>
       <c r="D73" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">요약·분류 병렬 실행 최적화</t>
@@ -4951,6 +5556,7 @@
     </row>
     <row r="74" spans="1:19" ht="18" customHeight="1">
       <c r="A74" s="4"/>
+      <c r="C74" s="5"/>
       <c r="D74" s="8"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
@@ -4966,11 +5572,28 @@
           <t xml:space="preserve">3.2</t>
         </is>
       </c>
+      <c r="B75" s="7"/>
       <c r="C75" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
+      <c r="K75" s="7"/>
+      <c r="L75" s="7"/>
+      <c r="M75" s="7"/>
+      <c r="N75" s="7"/>
+      <c r="O75" s="7"/>
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7"/>
+      <c r="S75" s="7"/>
     </row>
     <row r="76" spans="1:19" ht="18" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
@@ -4978,6 +5601,8 @@
           <t xml:space="preserve">3.2.1</t>
         </is>
       </c>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
       <c r="D76" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">분석 요청 / 진행 표시</t>
@@ -5013,6 +5638,15 @@
           <t xml:space="preserve">analyze 연동</t>
         </is>
       </c>
+      <c r="K76" s="5"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="10"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
     </row>
     <row r="77" spans="1:19" ht="18" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
@@ -5020,6 +5654,8 @@
           <t xml:space="preserve">3.2.2</t>
         </is>
       </c>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">요약 / 카테고리 결과 컴포넌트</t>
@@ -5055,6 +5691,15 @@
           <t xml:space="preserve">ResultView</t>
         </is>
       </c>
+      <c r="K77" s="5"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="10"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
     </row>
     <row r="78" spans="1:19" ht="18" customHeight="1">
       <c r="A78" s="4" t="inlineStr">
@@ -5062,6 +5707,7 @@
           <t xml:space="preserve">3.2.3</t>
         </is>
       </c>
+      <c r="C78" s="5"/>
       <c r="D78" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">메인 / 랜딩 페이지 구성</t>
@@ -5109,6 +5755,23 @@
           <t xml:space="preserve">조회 / 검색 / 출력  [C · 보현]</t>
         </is>
       </c>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="6"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="6"/>
     </row>
     <row r="80" spans="1:19" ht="18" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
@@ -5116,11 +5779,28 @@
           <t xml:space="preserve">4.1</t>
         </is>
       </c>
+      <c r="B80" s="7"/>
       <c r="C80" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">백엔드</t>
         </is>
       </c>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="M80" s="7"/>
+      <c r="N80" s="7"/>
+      <c r="O80" s="7"/>
+      <c r="P80" s="7"/>
+      <c r="Q80" s="7"/>
+      <c r="R80" s="7"/>
+      <c r="S80" s="7"/>
     </row>
     <row r="81" spans="1:19" ht="18" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
@@ -5128,6 +5808,8 @@
           <t xml:space="preserve">4.1.1</t>
         </is>
       </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
       <c r="D81" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">document_service.py</t>
@@ -5163,6 +5845,15 @@
           <t xml:space="preserve">서비스</t>
         </is>
       </c>
+      <c r="K81" s="5"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+      <c r="S81" s="4"/>
     </row>
     <row r="82" spans="1:19" ht="18" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
@@ -5170,6 +5861,8 @@
           <t xml:space="preserve">4.1.2</t>
         </is>
       </c>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">document_router.py — 목록/상세 (동기)</t>
@@ -5210,6 +5903,14 @@
           <t xml:space="preserve">PageResponse 사용</t>
         </is>
       </c>
+      <c r="L82" s="4"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4"/>
+      <c r="S82" s="4"/>
     </row>
     <row r="83" spans="1:19" ht="18" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
@@ -5217,6 +5918,8 @@
           <t xml:space="preserve">4.1.3</t>
         </is>
       </c>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
       <c r="D83" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">검색 (q / document_type / category)</t>
@@ -5257,6 +5960,14 @@
           <t xml:space="preserve">파일명 + 본문 부분검색. 공백 정규화 포함 (ISS-034)</t>
         </is>
       </c>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="10"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
     </row>
     <row r="84" spans="1:19" ht="18" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
@@ -5264,6 +5975,8 @@
           <t xml:space="preserve">4.1.4</t>
         </is>
       </c>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
       <c r="D84" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">다운로드 (.txt, 한글 파일명 대응)</t>
@@ -5304,6 +6017,14 @@
           <t xml:space="preserve">filename*=UTF-8''. 줄바꿈 버그 ISS-016 수정</t>
         </is>
       </c>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="10"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4"/>
+      <c r="S84" s="4"/>
     </row>
     <row r="85" spans="1:19" ht="18" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
@@ -5311,6 +6032,8 @@
           <t xml:space="preserve">4.1.5</t>
         </is>
       </c>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
       <c r="D85" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">삭제 (cascade + 업로드 파일 제거)</t>
@@ -5351,6 +6074,14 @@
           <t xml:space="preserve">결정사항 18 변경으로 구현. cascade + 업로드 파일 제거</t>
         </is>
       </c>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="4"/>
+      <c r="S85" s="4"/>
     </row>
     <row r="86" spans="1:19" ht="18" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
@@ -5358,11 +6089,28 @@
           <t xml:space="preserve">4.2</t>
         </is>
       </c>
+      <c r="B86" s="7"/>
       <c r="C86" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">프론트엔드</t>
         </is>
       </c>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
+      <c r="G86" s="7"/>
+      <c r="H86" s="7"/>
+      <c r="I86" s="7"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="7"/>
+      <c r="L86" s="7"/>
+      <c r="M86" s="7"/>
+      <c r="N86" s="7"/>
+      <c r="O86" s="7"/>
+      <c r="P86" s="7"/>
+      <c r="Q86" s="7"/>
+      <c r="R86" s="7"/>
+      <c r="S86" s="7"/>
     </row>
     <row r="87" spans="1:19" ht="18" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -5370,6 +6118,8 @@
           <t xml:space="preserve">4.2.1</t>
         </is>
       </c>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
       <c r="D87" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">목록 화면</t>
@@ -5410,6 +6160,14 @@
           <t xml:space="preserve">테이블 + 검색 + 페이징</t>
         </is>
       </c>
+      <c r="L87" s="4"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4"/>
+      <c r="S87" s="4"/>
     </row>
     <row r="88" spans="1:19" ht="18" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
@@ -5417,6 +6175,8 @@
           <t xml:space="preserve">4.2.2</t>
         </is>
       </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">상세 화면 (요약 + 카테고리)</t>
@@ -5457,6 +6217,14 @@
           <t xml:space="preserve">원문 접기·펼치기 + 분석 이력</t>
         </is>
       </c>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+      <c r="S88" s="4"/>
     </row>
     <row r="89" spans="1:19" ht="18" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
@@ -5464,6 +6232,8 @@
           <t xml:space="preserve">4.2.3</t>
         </is>
       </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">검색 UI + 다운로드 버튼</t>
@@ -5499,6 +6269,15 @@
           <t xml:space="preserve">SearchBar</t>
         </is>
       </c>
+      <c r="K89" s="5"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="10"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="4"/>
+      <c r="S89" s="4"/>
     </row>
     <row r="90" spans="1:19" ht="18" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
@@ -5506,6 +6285,7 @@
           <t xml:space="preserve">4.2.4</t>
         </is>
       </c>
+      <c r="C90" s="5"/>
       <c r="D90" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">공통 컴포넌트 + 디자인 토큰</t>
@@ -5553,6 +6333,7 @@
           <t xml:space="preserve">4.2.5</t>
         </is>
       </c>
+      <c r="C91" s="5"/>
       <c r="D91" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">App.jsx 라우터 통합</t>
@@ -5600,6 +6381,7 @@
           <t xml:space="preserve">4.2.6</t>
         </is>
       </c>
+      <c r="C92" s="5"/>
       <c r="D92" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">목록에 업로드 진입점 추가</t>
@@ -5647,6 +6429,7 @@
           <t xml:space="preserve">4.2.7</t>
         </is>
       </c>
+      <c r="C93" s="5"/>
       <c r="D93" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">목록 + 상세 패널 (마스터-디테일)</t>
@@ -5694,6 +6477,7 @@
           <t xml:space="preserve">4.2.8</t>
         </is>
       </c>
+      <c r="C94" s="5"/>
       <c r="D94" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">레이아웃 폭·여백 통일 및 헤더 정리</t>
@@ -5741,6 +6525,7 @@
           <t xml:space="preserve">4.2.9</t>
         </is>
       </c>
+      <c r="C95" s="5"/>
       <c r="D95" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">홈 화면 기능 설명 영역 구성</t>
@@ -5788,6 +6573,7 @@
           <t xml:space="preserve">4.2.10</t>
         </is>
       </c>
+      <c r="C96" s="5"/>
       <c r="D96" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">검색 공백 정규화</t>
@@ -5835,6 +6621,7 @@
           <t xml:space="preserve">4.2.11</t>
         </is>
       </c>
+      <c r="C97" s="5"/>
       <c r="D97" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">삭제 화면 (확인 창 · 목록 갱신)</t>
@@ -5877,6 +6664,7 @@
           <t xml:space="preserve">4.2.12</t>
         </is>
       </c>
+      <c r="C98" s="5"/>
       <c r="D98" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">UI/UX 전면 개선 및 공통 컴포넌트 리팩터링</t>
@@ -5924,6 +6712,7 @@
           <t xml:space="preserve">4.2.13</t>
         </is>
       </c>
+      <c r="C99" s="5"/>
       <c r="D99" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">정의되지 않은 경로 404 화면</t>
@@ -5976,6 +6765,23 @@
           <t xml:space="preserve">통합 / 테스트 / 배포</t>
         </is>
       </c>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="6"/>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
     </row>
     <row r="101" spans="1:19" ht="18" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -5983,11 +6789,28 @@
           <t xml:space="preserve">5.1</t>
         </is>
       </c>
+      <c r="B101" s="7"/>
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">통합</t>
         </is>
       </c>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
+      <c r="H101" s="7"/>
+      <c r="I101" s="7"/>
+      <c r="J101" s="7"/>
+      <c r="K101" s="7"/>
+      <c r="L101" s="7"/>
+      <c r="M101" s="7"/>
+      <c r="N101" s="7"/>
+      <c r="O101" s="7"/>
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="7"/>
+      <c r="S101" s="7"/>
     </row>
     <row r="102" spans="1:19" ht="18" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
@@ -5995,6 +6818,8 @@
           <t xml:space="preserve">5.1.1</t>
         </is>
       </c>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
       <c r="D102" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">★ 마일스톤: E2E 전 구간 관통</t>
@@ -6035,6 +6860,14 @@
           <t xml:space="preserve">08-03 관통 확인</t>
         </is>
       </c>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="20"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
     </row>
     <row r="103" spans="1:19" ht="18" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
@@ -6042,6 +6875,8 @@
           <t xml:space="preserve">5.1.2</t>
         </is>
       </c>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
       <c r="D103" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">API 계약 불일치 수정</t>
@@ -6082,6 +6917,14 @@
           <t xml:space="preserve">ISS-016 · ISS-017</t>
         </is>
       </c>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="10"/>
+      <c r="O103" s="10"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
     </row>
     <row r="104" spans="1:19" ht="18" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
@@ -6089,11 +6932,28 @@
           <t xml:space="preserve">5.2</t>
         </is>
       </c>
+      <c r="B104" s="7"/>
       <c r="C104" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">테스트</t>
         </is>
       </c>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="7"/>
+      <c r="I104" s="7"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="7"/>
+      <c r="L104" s="7"/>
+      <c r="M104" s="7"/>
+      <c r="N104" s="7"/>
+      <c r="O104" s="7"/>
+      <c r="P104" s="7"/>
+      <c r="Q104" s="7"/>
+      <c r="R104" s="7"/>
+      <c r="S104" s="7"/>
     </row>
     <row r="105" spans="1:19" ht="18" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
@@ -6101,6 +6961,8 @@
           <t xml:space="preserve">5.2.1</t>
         </is>
       </c>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
       <c r="D105" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">단위 테스트 작성 / 실행</t>
@@ -6141,6 +7003,14 @@
           <t xml:space="preserve">66항목 전 항목 판정 완료</t>
         </is>
       </c>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="10"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+      <c r="S105" s="4"/>
     </row>
     <row r="106" spans="1:19" ht="18" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
@@ -6148,6 +7018,8 @@
           <t xml:space="preserve">5.2.2</t>
         </is>
       </c>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
       <c r="D106" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">통합 테스트 시나리오 작성 / 실행</t>
@@ -6188,6 +7060,14 @@
           <t xml:space="preserve">44항목 중 29건 판정. 잔여 15건은 08-06 오전</t>
         </is>
       </c>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="10"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
     </row>
     <row r="107" spans="1:19" ht="18" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
@@ -6195,6 +7075,8 @@
           <t xml:space="preserve">5.2.3</t>
         </is>
       </c>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
       <c r="D107" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">에러 / 이슈 리포트 정리</t>
@@ -6235,6 +7117,14 @@
           <t xml:space="preserve">이슈관리 시트 46건 기록</t>
         </is>
       </c>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="10"/>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
     </row>
     <row r="108" spans="1:19" ht="18" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
@@ -6242,6 +7132,7 @@
           <t xml:space="preserve">5.2.4</t>
         </is>
       </c>
+      <c r="C108" s="5"/>
       <c r="D108" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">목록 조회 N+1 쿼리 실측 및 개선</t>
@@ -6289,6 +7180,7 @@
           <t xml:space="preserve">5.2.5</t>
         </is>
       </c>
+      <c r="C109" s="5"/>
       <c r="D109" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">OCR 엔진 정확도 비교 측정</t>
@@ -6336,6 +7228,7 @@
           <t xml:space="preserve">5.2.6</t>
         </is>
       </c>
+      <c r="C110" s="5"/>
       <c r="D110" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">산출물 파일 형식·인코딩 정리</t>
@@ -6383,11 +7276,28 @@
           <t xml:space="preserve">5.3</t>
         </is>
       </c>
+      <c r="B111" s="7"/>
       <c r="C111" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">배포</t>
         </is>
       </c>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
+      <c r="G111" s="7"/>
+      <c r="H111" s="7"/>
+      <c r="I111" s="7"/>
+      <c r="J111" s="7"/>
+      <c r="K111" s="7"/>
+      <c r="L111" s="7"/>
+      <c r="M111" s="7"/>
+      <c r="N111" s="7"/>
+      <c r="O111" s="7"/>
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="7"/>
+      <c r="S111" s="7"/>
     </row>
     <row r="112" spans="1:19" ht="18" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
@@ -6395,6 +7305,8 @@
           <t xml:space="preserve">5.3.1</t>
         </is>
       </c>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">프론트엔드 컨테이너 검증</t>
@@ -6430,6 +7342,15 @@
           <t xml:space="preserve">frontend Dockerfile</t>
         </is>
       </c>
+      <c r="K112" s="5"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="10"/>
+      <c r="Q112" s="10"/>
+      <c r="R112" s="4"/>
+      <c r="S112" s="4"/>
     </row>
     <row r="113" spans="1:19" ht="18" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
@@ -6437,6 +7358,8 @@
           <t xml:space="preserve">5.3.2</t>
         </is>
       </c>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
       <c r="D113" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">docker compose 전체 3컨테이너 기동 검증</t>
@@ -6477,6 +7400,14 @@
           <t xml:space="preserve">PaddleOCR 포함 이미지</t>
         </is>
       </c>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="10"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="4"/>
     </row>
     <row r="114" spans="1:19" ht="18" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
@@ -6484,6 +7415,8 @@
           <t xml:space="preserve">5.3.3</t>
         </is>
       </c>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">운영 메뉴얼 / 배포 문서</t>
@@ -6524,6 +7457,14 @@
           <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="10"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="4"/>
     </row>
     <row r="115" spans="1:19" ht="18" customHeight="1">
       <c r="A115" s="6" t="inlineStr">
@@ -6536,6 +7477,23 @@
           <t xml:space="preserve">산출물 / 발표 준비</t>
         </is>
       </c>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="6"/>
     </row>
     <row r="116" spans="1:19" ht="18" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
@@ -6543,11 +7501,28 @@
           <t xml:space="preserve">6.1</t>
         </is>
       </c>
+      <c r="B116" s="7"/>
       <c r="C116" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">문서 산출물</t>
         </is>
       </c>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
+      <c r="G116" s="7"/>
+      <c r="H116" s="7"/>
+      <c r="I116" s="7"/>
+      <c r="J116" s="7"/>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7"/>
+      <c r="M116" s="7"/>
+      <c r="N116" s="7"/>
+      <c r="O116" s="7"/>
+      <c r="P116" s="7"/>
+      <c r="Q116" s="7"/>
+      <c r="R116" s="7"/>
+      <c r="S116" s="7"/>
     </row>
     <row r="117" spans="1:19" ht="18" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
@@ -6555,6 +7530,8 @@
           <t xml:space="preserve">6.1.1</t>
         </is>
       </c>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">프로젝트 완료 보고서</t>
@@ -6595,6 +7572,14 @@
           <t xml:space="preserve">지시서 필수항목</t>
         </is>
       </c>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="10"/>
+      <c r="R117" s="10"/>
+      <c r="S117" s="4"/>
     </row>
     <row r="118" spans="1:19" ht="18" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
@@ -6602,6 +7587,8 @@
           <t xml:space="preserve">6.1.2</t>
         </is>
       </c>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
       <c r="D118" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">산출물 11종 최종 점검</t>
@@ -6637,6 +7624,15 @@
           <t xml:space="preserve">제출 목록</t>
         </is>
       </c>
+      <c r="K118" s="5"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="10"/>
+      <c r="S118" s="4"/>
     </row>
     <row r="119" spans="1:19" ht="18" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -6644,11 +7640,28 @@
           <t xml:space="preserve">6.2</t>
         </is>
       </c>
+      <c r="B119" s="7"/>
       <c r="C119" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">발표</t>
         </is>
       </c>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
+      <c r="H119" s="7"/>
+      <c r="I119" s="7"/>
+      <c r="J119" s="7"/>
+      <c r="K119" s="7"/>
+      <c r="L119" s="7"/>
+      <c r="M119" s="7"/>
+      <c r="N119" s="7"/>
+      <c r="O119" s="7"/>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7"/>
+      <c r="S119" s="7"/>
     </row>
     <row r="120" spans="1:19" ht="18" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
@@ -6656,6 +7669,8 @@
           <t xml:space="preserve">6.2.1</t>
         </is>
       </c>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
       <c r="D120" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">★ 코드 프리즈</t>
@@ -6696,6 +7711,14 @@
           <t xml:space="preserve">08-05 코드 프리즈. 이후 산출물 작업만 진행</t>
         </is>
       </c>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="20"/>
+      <c r="R120" s="4"/>
+      <c r="S120" s="4"/>
     </row>
     <row r="121" spans="1:19" ht="18" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
@@ -6703,6 +7726,8 @@
           <t xml:space="preserve">6.2.2</t>
         </is>
       </c>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
       <c r="D121" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">발표자료(PPT) 작성 — 목차 5장</t>
@@ -6743,6 +7768,14 @@
           <t xml:space="preserve">전원 분담</t>
         </is>
       </c>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="10"/>
+      <c r="R121" s="10"/>
+      <c r="S121" s="4"/>
     </row>
     <row r="122" spans="1:19" ht="18" customHeight="1">
       <c r="A122" s="4" t="inlineStr">
@@ -6750,6 +7783,8 @@
           <t xml:space="preserve">6.2.3</t>
         </is>
       </c>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">발표영상 녹화 / 편집</t>
@@ -6790,6 +7825,14 @@
           <t xml:space="preserve">시나리오 사전 작성</t>
         </is>
       </c>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="10"/>
+      <c r="R122" s="10"/>
+      <c r="S122" s="4"/>
     </row>
     <row r="123" spans="1:19" ht="18" customHeight="1">
       <c r="A123" s="4" t="inlineStr">
@@ -6797,6 +7840,8 @@
           <t xml:space="preserve">6.2.4</t>
         </is>
       </c>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
       <c r="D123" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">발표 리허설 2회 (시간 측정)</t>
@@ -6837,6 +7882,14 @@
           <t xml:space="preserve">전원 발표 필수</t>
         </is>
       </c>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="10"/>
+      <c r="S123" s="4"/>
     </row>
     <row r="124" spans="1:19" ht="18" customHeight="1">
       <c r="A124" s="4" t="inlineStr">
@@ -6844,6 +7897,8 @@
           <t xml:space="preserve">6.2.5</t>
         </is>
       </c>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
       <c r="D124" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">★ 최종 발표</t>
@@ -6884,6 +7939,14 @@
           <t xml:space="preserve">팀원 전원 참여</t>
         </is>
       </c>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4"/>
+      <c r="S124" s="20"/>
     </row>
     <row r="125" spans="1:19" ht="18" customHeight="1"/>
     <row r="126" spans="1:19" ht="18" customHeight="1"/>

--- a/관리/WBS(작업분할구조도)_v1.xlsx
+++ b/관리/WBS(작업분할구조도)_v1.xlsx
@@ -9115,11 +9115,15 @@
       <c r="E13" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>149</v>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진행중</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목차 5장 + 추천 2장 · 24슬라이드 초안 완성</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:7" ht="18" customHeight="1">
